--- a/research/traditional_assets/database/data/jordan/jordan_transportation.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_transportation.xlsx
@@ -1626,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1763,22 +1763,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1206693399797759</v>
+        <v>0.1204640012998163</v>
       </c>
       <c r="C2">
-        <v>15.01721206762781</v>
+        <v>14.8855212890846</v>
       </c>
       <c r="D2">
-        <v>13.86721206762781</v>
+        <v>13.8839212890846</v>
       </c>
       <c r="E2">
-        <v>-2.74</v>
+        <v>-2.5916</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1484</v>
       </c>
       <c r="G2">
         <v>1.15</v>
@@ -1799,28 +1799,28 @@
         <v>3.723</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00746452</v>
       </c>
       <c r="N2">
-        <v>3.723</v>
+        <v>3.71553548</v>
       </c>
       <c r="O2">
-        <v>0.7446</v>
+        <v>0.743107096</v>
       </c>
       <c r="P2">
-        <v>2.9784</v>
+        <v>2.972428384</v>
       </c>
       <c r="Q2">
-        <v>2.9854</v>
+        <v>2.979428384</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1206693399797759</v>
+        <v>0.1212743447472892</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185859</v>
+        <v>0.8264750100997462</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>498.7594647746942</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1845,22 +1845,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1204640012998163</v>
+        <v>0.1202586626198567</v>
       </c>
       <c r="C3">
-        <v>14.8855212890846</v>
+        <v>14.75387082649019</v>
       </c>
       <c r="D3">
-        <v>13.8839212890846</v>
+        <v>13.90067082649019</v>
       </c>
       <c r="E3">
-        <v>-2.5916</v>
+        <v>-2.4432</v>
       </c>
       <c r="F3">
-        <v>0.1484</v>
+        <v>0.2968</v>
       </c>
       <c r="G3">
         <v>1.15</v>
@@ -1881,28 +1881,28 @@
         <v>3.723</v>
       </c>
       <c r="M3">
-        <v>0.00746452</v>
+        <v>0.01492904</v>
       </c>
       <c r="N3">
-        <v>3.71553548</v>
+        <v>3.70807096</v>
       </c>
       <c r="O3">
-        <v>0.743107096</v>
+        <v>0.741614192</v>
       </c>
       <c r="P3">
-        <v>2.972428384</v>
+        <v>2.966456768</v>
       </c>
       <c r="Q3">
-        <v>2.979428384</v>
+        <v>2.973456768</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1212743447472892</v>
+        <v>0.1218916965508742</v>
       </c>
       <c r="T3">
-        <v>0.8264750100997462</v>
+        <v>0.8332352653866444</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>498.7594647746942</v>
+        <v>249.3797323873471</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1927,22 +1927,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1202586626198567</v>
+        <v>0.1200533239398972</v>
       </c>
       <c r="C4">
-        <v>14.75387082649019</v>
+        <v>14.62226082593206</v>
       </c>
       <c r="D4">
-        <v>13.90067082649019</v>
+        <v>13.91746082593206</v>
       </c>
       <c r="E4">
-        <v>-2.4432</v>
+        <v>-2.2948</v>
       </c>
       <c r="F4">
-        <v>0.2968</v>
+        <v>0.4452</v>
       </c>
       <c r="G4">
         <v>1.15</v>
@@ -1963,28 +1963,28 @@
         <v>3.723</v>
       </c>
       <c r="M4">
-        <v>0.01492904</v>
+        <v>0.02239356</v>
       </c>
       <c r="N4">
-        <v>3.70807096</v>
+        <v>3.70060644</v>
       </c>
       <c r="O4">
-        <v>0.741614192</v>
+        <v>0.7401212880000001</v>
       </c>
       <c r="P4">
-        <v>2.966456768</v>
+        <v>2.960485152</v>
       </c>
       <c r="Q4">
-        <v>2.973456768</v>
+        <v>2.967485152</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1218916965508742</v>
+        <v>0.122521777257626</v>
       </c>
       <c r="T4">
-        <v>0.8332352653866444</v>
+        <v>0.840134907380489</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>249.3797323873471</v>
+        <v>166.2531549248981</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2009,22 +2009,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1200533239398972</v>
+        <v>0.1198479852599376</v>
       </c>
       <c r="C5">
-        <v>14.62226082593206</v>
+        <v>14.49069143420438</v>
       </c>
       <c r="D5">
-        <v>13.91746082593206</v>
+        <v>13.93429143420438</v>
       </c>
       <c r="E5">
-        <v>-2.2948</v>
+        <v>-2.1464</v>
       </c>
       <c r="F5">
-        <v>0.4452</v>
+        <v>0.5936</v>
       </c>
       <c r="G5">
         <v>1.15</v>
@@ -2045,28 +2045,28 @@
         <v>3.723</v>
       </c>
       <c r="M5">
-        <v>0.02239356</v>
+        <v>0.02985808</v>
       </c>
       <c r="N5">
-        <v>3.70060644</v>
+        <v>3.69314192</v>
       </c>
       <c r="O5">
-        <v>0.7401212880000001</v>
+        <v>0.7386283840000001</v>
       </c>
       <c r="P5">
-        <v>2.960485152</v>
+        <v>2.954513536</v>
       </c>
       <c r="Q5">
-        <v>2.967485152</v>
+        <v>2.961513536</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.122521777257626</v>
+        <v>0.1231649846457684</v>
       </c>
       <c r="T5">
-        <v>0.840134907380489</v>
+        <v>0.8471782919158721</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>166.2531549248981</v>
+        <v>124.6898661936735</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2091,22 +2091,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1198479852599376</v>
+        <v>0.1196426465799781</v>
       </c>
       <c r="C6">
-        <v>14.49069143420438</v>
+        <v>14.35916279881226</v>
       </c>
       <c r="D6">
-        <v>13.93429143420438</v>
+        <v>13.95116279881226</v>
       </c>
       <c r="E6">
-        <v>-2.1464</v>
+        <v>-1.998</v>
       </c>
       <c r="F6">
-        <v>0.5936</v>
+        <v>0.742</v>
       </c>
       <c r="G6">
         <v>1.15</v>
@@ -2127,28 +2127,28 @@
         <v>3.723</v>
       </c>
       <c r="M6">
-        <v>0.02985808</v>
+        <v>0.0373226</v>
       </c>
       <c r="N6">
-        <v>3.69314192</v>
+        <v>3.6856774</v>
       </c>
       <c r="O6">
-        <v>0.7386283840000001</v>
+        <v>0.7371354800000001</v>
       </c>
       <c r="P6">
-        <v>2.954513536</v>
+        <v>2.94854192</v>
       </c>
       <c r="Q6">
-        <v>2.961513536</v>
+        <v>2.95554192</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1231649846457684</v>
+        <v>0.1238217332420822</v>
       </c>
       <c r="T6">
-        <v>0.8471782919158721</v>
+        <v>0.8543699582309473</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>124.6898661936735</v>
+        <v>99.75189295493884</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2173,22 +2173,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1196426465799781</v>
+        <v>0.1194373079000185</v>
       </c>
       <c r="C7">
-        <v>14.35916279881226</v>
+        <v>14.22767506797605</v>
       </c>
       <c r="D7">
-        <v>13.95116279881226</v>
+        <v>13.96807506797605</v>
       </c>
       <c r="E7">
-        <v>-1.998</v>
+        <v>-1.8496</v>
       </c>
       <c r="F7">
-        <v>0.742</v>
+        <v>0.8904000000000001</v>
       </c>
       <c r="G7">
         <v>1.15</v>
@@ -2209,28 +2209,28 @@
         <v>3.723</v>
       </c>
       <c r="M7">
-        <v>0.0373226</v>
+        <v>0.04478712</v>
       </c>
       <c r="N7">
-        <v>3.6856774</v>
+        <v>3.67821288</v>
       </c>
       <c r="O7">
-        <v>0.7371354800000001</v>
+        <v>0.735642576</v>
       </c>
       <c r="P7">
-        <v>2.94854192</v>
+        <v>2.942570304</v>
       </c>
       <c r="Q7">
-        <v>2.95554192</v>
+        <v>2.949570304</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1238217332420822</v>
+        <v>0.1244924552127857</v>
       </c>
       <c r="T7">
-        <v>0.8543699582309473</v>
+        <v>0.8617146387229393</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>99.75189295493884</v>
+        <v>83.12657746244902</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2255,22 +2255,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1194373079000185</v>
+        <v>0.119231969220059</v>
       </c>
       <c r="C8">
-        <v>14.22767506797605</v>
+        <v>14.09622839063571</v>
       </c>
       <c r="D8">
-        <v>13.96807506797605</v>
+        <v>13.98502839063571</v>
       </c>
       <c r="E8">
-        <v>-1.8496</v>
+        <v>-1.7012</v>
       </c>
       <c r="F8">
-        <v>0.8904</v>
+        <v>1.0388</v>
       </c>
       <c r="G8">
         <v>1.15</v>
@@ -2291,28 +2291,28 @@
         <v>3.723</v>
       </c>
       <c r="M8">
-        <v>0.04478711999999999</v>
+        <v>0.05225164</v>
       </c>
       <c r="N8">
-        <v>3.67821288</v>
+        <v>3.67074836</v>
       </c>
       <c r="O8">
-        <v>0.735642576</v>
+        <v>0.734149672</v>
       </c>
       <c r="P8">
-        <v>2.942570304</v>
+        <v>2.936598688</v>
       </c>
       <c r="Q8">
-        <v>2.949570304</v>
+        <v>2.943598688</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1244924552127857</v>
+        <v>0.1251776013118914</v>
       </c>
       <c r="T8">
-        <v>0.8617146387229393</v>
+        <v>0.8692172693330384</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>83.12657746244903</v>
+        <v>71.2513521106706</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2337,22 +2337,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.119231969220059</v>
+        <v>0.1190266305400994</v>
       </c>
       <c r="C9">
-        <v>14.09622839063571</v>
+        <v>13.96482291645516</v>
       </c>
       <c r="D9">
-        <v>13.98502839063571</v>
+        <v>14.00202291645516</v>
       </c>
       <c r="E9">
-        <v>-1.7012</v>
+        <v>-1.5528</v>
       </c>
       <c r="F9">
-        <v>1.0388</v>
+        <v>1.1872</v>
       </c>
       <c r="G9">
         <v>1.15</v>
@@ -2373,28 +2373,28 @@
         <v>3.723</v>
       </c>
       <c r="M9">
-        <v>0.05225164000000001</v>
+        <v>0.05971616</v>
       </c>
       <c r="N9">
-        <v>3.67074836</v>
+        <v>3.66328384</v>
       </c>
       <c r="O9">
-        <v>0.734149672</v>
+        <v>0.732656768</v>
       </c>
       <c r="P9">
-        <v>2.936598688</v>
+        <v>2.930627072</v>
       </c>
       <c r="Q9">
-        <v>2.943598688</v>
+        <v>2.937627072</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1251776013118914</v>
+        <v>0.1258776418914124</v>
       </c>
       <c r="T9">
-        <v>0.8692172693330384</v>
+        <v>0.8768830006085745</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>71.25135211067058</v>
+        <v>62.34493309683678</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1190266305400994</v>
+        <v>0.1188212918601399</v>
       </c>
       <c r="C10">
-        <v>13.96482291645516</v>
+        <v>13.83345879582667</v>
       </c>
       <c r="D10">
-        <v>14.00202291645516</v>
+        <v>14.01905879582667</v>
       </c>
       <c r="E10">
-        <v>-1.5528</v>
+        <v>-1.4044</v>
       </c>
       <c r="F10">
-        <v>1.1872</v>
+        <v>1.3356</v>
       </c>
       <c r="G10">
         <v>1.15</v>
@@ -2455,28 +2455,28 @@
         <v>3.723</v>
       </c>
       <c r="M10">
-        <v>0.05971616</v>
+        <v>0.06718067999999999</v>
       </c>
       <c r="N10">
-        <v>3.66328384</v>
+        <v>3.65581932</v>
       </c>
       <c r="O10">
-        <v>0.732656768</v>
+        <v>0.731163864</v>
       </c>
       <c r="P10">
-        <v>2.930627072</v>
+        <v>2.924655456</v>
       </c>
       <c r="Q10">
-        <v>2.937627072</v>
+        <v>2.931655456</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1258776418914124</v>
+        <v>0.1265930679781757</v>
       </c>
       <c r="T10">
-        <v>0.8768830006085745</v>
+        <v>0.8847172094945619</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>62.34493309683678</v>
+        <v>55.41771830829936</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2501,22 +2501,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1188212918601399</v>
+        <v>0.1186159531801803</v>
       </c>
       <c r="C11">
-        <v>13.83345879582667</v>
+        <v>13.70213617987533</v>
       </c>
       <c r="D11">
-        <v>14.01905879582667</v>
+        <v>14.03613617987533</v>
       </c>
       <c r="E11">
-        <v>-1.4044</v>
+        <v>-1.256</v>
       </c>
       <c r="F11">
-        <v>1.3356</v>
+        <v>1.484</v>
       </c>
       <c r="G11">
         <v>1.15</v>
@@ -2537,28 +2537,28 @@
         <v>3.723</v>
       </c>
       <c r="M11">
-        <v>0.06718067999999999</v>
+        <v>0.07464519999999998</v>
       </c>
       <c r="N11">
-        <v>3.65581932</v>
+        <v>3.6483548</v>
       </c>
       <c r="O11">
-        <v>0.731163864</v>
+        <v>0.72967096</v>
       </c>
       <c r="P11">
-        <v>2.924655456</v>
+        <v>2.91868384</v>
       </c>
       <c r="Q11">
-        <v>2.931655456</v>
+        <v>2.92568384</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1265930679781757</v>
+        <v>0.1273243924224226</v>
       </c>
       <c r="T11">
-        <v>0.8847172094945619</v>
+        <v>0.892725511911349</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>55.41771830829936</v>
+        <v>49.87594647746943</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2583,22 +2583,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1186159531801804</v>
+        <v>0.1184106145002208</v>
       </c>
       <c r="C12">
-        <v>13.70213617987533</v>
+        <v>13.5708552204635</v>
       </c>
       <c r="D12">
-        <v>14.03613617987533</v>
+        <v>14.0532552204635</v>
       </c>
       <c r="E12">
-        <v>-1.256</v>
+        <v>-1.1076</v>
       </c>
       <c r="F12">
-        <v>1.484</v>
+        <v>1.6324</v>
       </c>
       <c r="G12">
         <v>1.15</v>
@@ -2619,28 +2619,28 @@
         <v>3.723</v>
       </c>
       <c r="M12">
-        <v>0.07464519999999999</v>
+        <v>0.08210972</v>
       </c>
       <c r="N12">
-        <v>3.6483548</v>
+        <v>3.64089028</v>
       </c>
       <c r="O12">
-        <v>0.72967096</v>
+        <v>0.728178056</v>
       </c>
       <c r="P12">
-        <v>2.91868384</v>
+        <v>2.912712224</v>
       </c>
       <c r="Q12">
-        <v>2.92568384</v>
+        <v>2.919712224</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1273243924224226</v>
+        <v>0.1280721511238436</v>
       </c>
       <c r="T12">
-        <v>0.8927255119113492</v>
+        <v>0.9009137761801989</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>49.87594647746942</v>
+        <v>45.34176952497219</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2665,22 +2665,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1184106145002208</v>
+        <v>0.1182052758202612</v>
       </c>
       <c r="C13">
-        <v>13.5708552204635</v>
+        <v>13.43961607019531</v>
       </c>
       <c r="D13">
-        <v>14.0532552204635</v>
+        <v>14.07041607019531</v>
       </c>
       <c r="E13">
-        <v>-1.1076</v>
+        <v>-0.9592000000000003</v>
       </c>
       <c r="F13">
-        <v>1.6324</v>
+        <v>1.7808</v>
       </c>
       <c r="G13">
         <v>1.15</v>
@@ -2701,28 +2701,28 @@
         <v>3.723</v>
       </c>
       <c r="M13">
-        <v>0.08210972</v>
+        <v>0.08957423999999999</v>
       </c>
       <c r="N13">
-        <v>3.64089028</v>
+        <v>3.63342576</v>
       </c>
       <c r="O13">
-        <v>0.728178056</v>
+        <v>0.7266851519999999</v>
       </c>
       <c r="P13">
-        <v>2.912712224</v>
+        <v>2.906740608</v>
       </c>
       <c r="Q13">
-        <v>2.919712224</v>
+        <v>2.913740608</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1280721511238436</v>
+        <v>0.128836904341206</v>
       </c>
       <c r="T13">
-        <v>0.9009137761801989</v>
+        <v>0.9092881373642498</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>45.34176952497219</v>
+        <v>41.56328873122452</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2747,22 +2747,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1182052758202612</v>
+        <v>0.1179999371403017</v>
       </c>
       <c r="C14">
-        <v>13.43961607019531</v>
+        <v>13.30841888242121</v>
       </c>
       <c r="D14">
-        <v>14.07041607019531</v>
+        <v>14.08761888242121</v>
       </c>
       <c r="E14">
-        <v>-0.9592000000000003</v>
+        <v>-0.8108000000000002</v>
       </c>
       <c r="F14">
-        <v>1.7808</v>
+        <v>1.9292</v>
       </c>
       <c r="G14">
         <v>1.15</v>
@@ -2783,28 +2783,28 @@
         <v>3.723</v>
       </c>
       <c r="M14">
-        <v>0.08957423999999999</v>
+        <v>0.09703876</v>
       </c>
       <c r="N14">
-        <v>3.63342576</v>
+        <v>3.62596124</v>
       </c>
       <c r="O14">
-        <v>0.7266851519999999</v>
+        <v>0.7251922479999999</v>
       </c>
       <c r="P14">
-        <v>2.906740608</v>
+        <v>2.900768992</v>
       </c>
       <c r="Q14">
-        <v>2.913740608</v>
+        <v>2.907768992</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.128836904341206</v>
+        <v>0.1296192380923008</v>
       </c>
       <c r="T14">
-        <v>0.9092881373642498</v>
+        <v>0.9178550125985088</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>41.56328873122452</v>
+        <v>38.36611267497647</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2829,22 +2829,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1179999371403017</v>
+        <v>0.1177945984603421</v>
       </c>
       <c r="C15">
-        <v>13.30841888242121</v>
+        <v>13.17726381124252</v>
       </c>
       <c r="D15">
-        <v>14.08761888242121</v>
+        <v>14.10486381124252</v>
       </c>
       <c r="E15">
-        <v>-0.8108000000000002</v>
+        <v>-0.6623999999999999</v>
       </c>
       <c r="F15">
-        <v>1.9292</v>
+        <v>2.0776</v>
       </c>
       <c r="G15">
         <v>1.15</v>
@@ -2865,28 +2865,28 @@
         <v>3.723</v>
       </c>
       <c r="M15">
-        <v>0.09703876</v>
+        <v>0.10450328</v>
       </c>
       <c r="N15">
-        <v>3.62596124</v>
+        <v>3.61849672</v>
       </c>
       <c r="O15">
-        <v>0.7251922479999999</v>
+        <v>0.723699344</v>
       </c>
       <c r="P15">
-        <v>2.900768992</v>
+        <v>2.894797376</v>
       </c>
       <c r="Q15">
-        <v>2.907768992</v>
+        <v>2.901797376</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1296192380923008</v>
+        <v>0.1304197656515606</v>
       </c>
       <c r="T15">
-        <v>0.9178550125985088</v>
+        <v>0.9266211174893785</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>38.36611267497647</v>
+        <v>35.62567605533529</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2911,22 +2911,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1177945984603421</v>
+        <v>0.1175892597803826</v>
       </c>
       <c r="C16">
-        <v>13.17726381124252</v>
+        <v>13.04615101151603</v>
       </c>
       <c r="D16">
-        <v>14.10486381124252</v>
+        <v>14.12215101151603</v>
       </c>
       <c r="E16">
-        <v>-0.6623999999999999</v>
+        <v>-0.5139999999999998</v>
       </c>
       <c r="F16">
-        <v>2.0776</v>
+        <v>2.226</v>
       </c>
       <c r="G16">
         <v>1.15</v>
@@ -2947,28 +2947,28 @@
         <v>3.723</v>
       </c>
       <c r="M16">
-        <v>0.10450328</v>
+        <v>0.1119678</v>
       </c>
       <c r="N16">
-        <v>3.61849672</v>
+        <v>3.6110322</v>
       </c>
       <c r="O16">
-        <v>0.723699344</v>
+        <v>0.72220644</v>
       </c>
       <c r="P16">
-        <v>2.894797376</v>
+        <v>2.88882576</v>
       </c>
       <c r="Q16">
-        <v>2.901797376</v>
+        <v>2.89582576</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1304197656515606</v>
+        <v>0.1312391291533913</v>
       </c>
       <c r="T16">
-        <v>0.9266211174893785</v>
+        <v>0.935593483671798</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>35.62567605533529</v>
+        <v>33.2506309849796</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2993,22 +2993,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1175892597803826</v>
+        <v>0.117383921100423</v>
       </c>
       <c r="C17">
-        <v>13.04615101151603</v>
+        <v>12.91508063885866</v>
       </c>
       <c r="D17">
-        <v>14.12215101151603</v>
+        <v>14.13948063885866</v>
       </c>
       <c r="E17">
-        <v>-0.5140000000000002</v>
+        <v>-0.3656000000000001</v>
       </c>
       <c r="F17">
-        <v>2.226</v>
+        <v>2.3744</v>
       </c>
       <c r="G17">
         <v>1.15</v>
@@ -3029,28 +3029,28 @@
         <v>3.723</v>
       </c>
       <c r="M17">
-        <v>0.1119678</v>
+        <v>0.11943232</v>
       </c>
       <c r="N17">
-        <v>3.6110322</v>
+        <v>3.60356768</v>
       </c>
       <c r="O17">
-        <v>0.72220644</v>
+        <v>0.720713536</v>
       </c>
       <c r="P17">
-        <v>2.88882576</v>
+        <v>2.882854144</v>
       </c>
       <c r="Q17">
-        <v>2.89582576</v>
+        <v>2.889854144</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1312391291533913</v>
+        <v>0.1320780013100274</v>
       </c>
       <c r="T17">
-        <v>0.935593483671798</v>
+        <v>0.9447794776204655</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>33.25063098497961</v>
+        <v>31.17246654841838</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3075,22 +3075,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.117383921100423</v>
+        <v>0.1171785824204635</v>
       </c>
       <c r="C18">
-        <v>12.91508063885866</v>
+        <v>12.78405284965211</v>
       </c>
       <c r="D18">
-        <v>14.13948063885866</v>
+        <v>14.15685284965211</v>
       </c>
       <c r="E18">
-        <v>-0.3656000000000001</v>
+        <v>-0.2172000000000001</v>
       </c>
       <c r="F18">
-        <v>2.3744</v>
+        <v>2.5228</v>
       </c>
       <c r="G18">
         <v>1.15</v>
@@ -3111,28 +3111,28 @@
         <v>3.723</v>
       </c>
       <c r="M18">
-        <v>0.11943232</v>
+        <v>0.12689684</v>
       </c>
       <c r="N18">
-        <v>3.60356768</v>
+        <v>3.59610316</v>
       </c>
       <c r="O18">
-        <v>0.720713536</v>
+        <v>0.719220632</v>
       </c>
       <c r="P18">
-        <v>2.882854144</v>
+        <v>2.876882528</v>
       </c>
       <c r="Q18">
-        <v>2.889854144</v>
+        <v>2.883882528</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1320780013100274</v>
+        <v>0.1329370872535705</v>
       </c>
       <c r="T18">
-        <v>0.9447794776204655</v>
+        <v>0.9541868208209083</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>31.17246654841838</v>
+        <v>29.33879204557024</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3157,22 +3157,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1171785824204635</v>
+        <v>0.1169732437405039</v>
       </c>
       <c r="C19">
-        <v>12.78405284965211</v>
+        <v>12.65306780104755</v>
       </c>
       <c r="D19">
-        <v>14.15685284965211</v>
+        <v>14.17426780104755</v>
       </c>
       <c r="E19">
-        <v>-0.2172000000000001</v>
+        <v>-0.06879999999999997</v>
       </c>
       <c r="F19">
-        <v>2.5228</v>
+        <v>2.6712</v>
       </c>
       <c r="G19">
         <v>1.15</v>
@@ -3193,28 +3193,28 @@
         <v>3.723</v>
       </c>
       <c r="M19">
-        <v>0.12689684</v>
+        <v>0.13436136</v>
       </c>
       <c r="N19">
-        <v>3.59610316</v>
+        <v>3.58863864</v>
       </c>
       <c r="O19">
-        <v>0.719220632</v>
+        <v>0.717727728</v>
       </c>
       <c r="P19">
-        <v>2.876882528</v>
+        <v>2.870910912</v>
       </c>
       <c r="Q19">
-        <v>2.883882528</v>
+        <v>2.877910912</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1329370872535705</v>
+        <v>0.1338171265128097</v>
       </c>
       <c r="T19">
-        <v>0.9541868208209083</v>
+        <v>0.963823611416484</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.33879204557024</v>
+        <v>27.70885915414967</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3239,22 +3239,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1169732437405039</v>
+        <v>0.1167679050605444</v>
       </c>
       <c r="C20">
-        <v>12.65306780104756</v>
+        <v>12.52212565097041</v>
       </c>
       <c r="D20">
-        <v>14.17426780104755</v>
+        <v>14.19172565097041</v>
       </c>
       <c r="E20">
-        <v>-0.06880000000000042</v>
+        <v>0.07959999999999967</v>
       </c>
       <c r="F20">
-        <v>2.6712</v>
+        <v>2.8196</v>
       </c>
       <c r="G20">
         <v>1.15</v>
@@ -3275,28 +3275,28 @@
         <v>3.723</v>
       </c>
       <c r="M20">
-        <v>0.13436136</v>
+        <v>0.14182588</v>
       </c>
       <c r="N20">
-        <v>3.58863864</v>
+        <v>3.58117412</v>
       </c>
       <c r="O20">
-        <v>0.7177277280000001</v>
+        <v>0.716234824</v>
       </c>
       <c r="P20">
-        <v>2.870910912</v>
+        <v>2.864939296</v>
       </c>
       <c r="Q20">
-        <v>2.877910912</v>
+        <v>2.871939296</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1338171265128097</v>
+        <v>0.1347188951364745</v>
       </c>
       <c r="T20">
-        <v>0.9638236114164839</v>
+        <v>0.9736983474588639</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>27.70885915414968</v>
+        <v>26.25049814603654</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3321,22 +3321,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1167679050605444</v>
+        <v>0.1165625663805848</v>
       </c>
       <c r="C21">
-        <v>12.52212565097041</v>
+        <v>12.39122655812508</v>
       </c>
       <c r="D21">
-        <v>14.19172565097041</v>
+        <v>14.20922655812508</v>
       </c>
       <c r="E21">
-        <v>0.07959999999999967</v>
+        <v>0.2279999999999998</v>
       </c>
       <c r="F21">
-        <v>2.8196</v>
+        <v>2.968</v>
       </c>
       <c r="G21">
         <v>1.15</v>
@@ -3357,28 +3357,28 @@
         <v>3.723</v>
       </c>
       <c r="M21">
-        <v>0.14182588</v>
+        <v>0.1492904</v>
       </c>
       <c r="N21">
-        <v>3.58117412</v>
+        <v>3.5737096</v>
       </c>
       <c r="O21">
-        <v>0.716234824</v>
+        <v>0.71474192</v>
       </c>
       <c r="P21">
-        <v>2.864939296</v>
+        <v>2.85896768</v>
       </c>
       <c r="Q21">
-        <v>2.871939296</v>
+        <v>2.86596768</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1347188951364745</v>
+        <v>0.135643207975731</v>
       </c>
       <c r="T21">
-        <v>0.9736983474588639</v>
+        <v>0.983819951902303</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.25049814603654</v>
+        <v>24.93797323873471</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3403,22 +3403,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1165625663805848</v>
+        <v>0.1163572277006253</v>
       </c>
       <c r="C22">
-        <v>12.39122655812508</v>
+        <v>12.26037068199979</v>
       </c>
       <c r="D22">
-        <v>14.20922655812508</v>
+        <v>14.22677068199979</v>
       </c>
       <c r="E22">
-        <v>0.2279999999999998</v>
+        <v>0.3763999999999998</v>
       </c>
       <c r="F22">
-        <v>2.968</v>
+        <v>3.1164</v>
       </c>
       <c r="G22">
         <v>1.15</v>
@@ -3439,28 +3439,28 @@
         <v>3.723</v>
       </c>
       <c r="M22">
-        <v>0.1492904</v>
+        <v>0.15675492</v>
       </c>
       <c r="N22">
-        <v>3.5737096</v>
+        <v>3.56624508</v>
       </c>
       <c r="O22">
-        <v>0.71474192</v>
+        <v>0.713249016</v>
       </c>
       <c r="P22">
-        <v>2.85896768</v>
+        <v>2.852996064</v>
       </c>
       <c r="Q22">
-        <v>2.86596768</v>
+        <v>2.859996064</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.135643207975731</v>
+        <v>0.136590921140032</v>
       </c>
       <c r="T22">
-        <v>0.983819951902303</v>
+        <v>0.9941977994962092</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>24.93797323873471</v>
+        <v>23.75045070355687</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1163572277006253</v>
+        <v>0.1161518890206657</v>
       </c>
       <c r="C23">
-        <v>12.26037068199979</v>
+        <v>12.1295581828714</v>
       </c>
       <c r="D23">
-        <v>14.22677068199979</v>
+        <v>14.2443581828714</v>
       </c>
       <c r="E23">
-        <v>0.3763999999999998</v>
+        <v>0.5247999999999999</v>
       </c>
       <c r="F23">
-        <v>3.1164</v>
+        <v>3.2648</v>
       </c>
       <c r="G23">
         <v>1.15</v>
@@ -3521,28 +3521,28 @@
         <v>3.723</v>
       </c>
       <c r="M23">
-        <v>0.15675492</v>
+        <v>0.16421944</v>
       </c>
       <c r="N23">
-        <v>3.56624508</v>
+        <v>3.55878056</v>
       </c>
       <c r="O23">
-        <v>0.713249016</v>
+        <v>0.711756112</v>
       </c>
       <c r="P23">
-        <v>2.852996064</v>
+        <v>2.847024448</v>
       </c>
       <c r="Q23">
-        <v>2.859996064</v>
+        <v>2.854024448</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.136590921140032</v>
+        <v>0.1375629346418791</v>
       </c>
       <c r="T23">
-        <v>0.9941977994962092</v>
+        <v>1.004841745746369</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>23.75045070355687</v>
+        <v>22.6708847624861</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3567,22 +3567,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1161518890206657</v>
+        <v>0.1159465503407062</v>
       </c>
       <c r="C24">
-        <v>12.1295581828714</v>
+        <v>11.99878922181033</v>
       </c>
       <c r="D24">
-        <v>14.2443581828714</v>
+        <v>14.26198922181033</v>
       </c>
       <c r="E24">
-        <v>0.5247999999999999</v>
+        <v>0.6732</v>
       </c>
       <c r="F24">
-        <v>3.2648</v>
+        <v>3.4132</v>
       </c>
       <c r="G24">
         <v>1.15</v>
@@ -3603,28 +3603,28 @@
         <v>3.723</v>
       </c>
       <c r="M24">
-        <v>0.16421944</v>
+        <v>0.17168396</v>
       </c>
       <c r="N24">
-        <v>3.55878056</v>
+        <v>3.55131604</v>
       </c>
       <c r="O24">
-        <v>0.711756112</v>
+        <v>0.710263208</v>
       </c>
       <c r="P24">
-        <v>2.847024448</v>
+        <v>2.841052832</v>
       </c>
       <c r="Q24">
-        <v>2.854024448</v>
+        <v>2.848052832</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1375629346418791</v>
+        <v>0.1385601952476704</v>
       </c>
       <c r="T24">
-        <v>1.004841745746369</v>
+        <v>1.015762158132897</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.6708847624861</v>
+        <v>21.68519412063888</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3649,22 +3649,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1159465503407062</v>
+        <v>0.1157412116607466</v>
       </c>
       <c r="C25">
-        <v>11.99878922181033</v>
+        <v>11.86806396068543</v>
       </c>
       <c r="D25">
-        <v>14.26198922181033</v>
+        <v>14.27966396068543</v>
       </c>
       <c r="E25">
-        <v>0.6732</v>
+        <v>0.8216000000000001</v>
       </c>
       <c r="F25">
-        <v>3.4132</v>
+        <v>3.5616</v>
       </c>
       <c r="G25">
         <v>1.15</v>
@@ -3685,28 +3685,28 @@
         <v>3.723</v>
       </c>
       <c r="M25">
-        <v>0.17168396</v>
+        <v>0.17914848</v>
       </c>
       <c r="N25">
-        <v>3.55131604</v>
+        <v>3.54385152</v>
       </c>
       <c r="O25">
-        <v>0.710263208</v>
+        <v>0.7087703040000001</v>
       </c>
       <c r="P25">
-        <v>2.841052832</v>
+        <v>2.835081216</v>
       </c>
       <c r="Q25">
-        <v>2.848052832</v>
+        <v>2.842081216</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1385601952476704</v>
+        <v>0.139583699553614</v>
       </c>
       <c r="T25">
-        <v>1.015762158132897</v>
+        <v>1.026969949792755</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.68519412063888</v>
+        <v>20.78164436561226</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3731,22 +3731,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1157412116607466</v>
+        <v>0.1155358729807871</v>
       </c>
       <c r="C26">
-        <v>11.86806396068543</v>
+        <v>11.73738256216896</v>
       </c>
       <c r="D26">
-        <v>14.27966396068543</v>
+        <v>14.29738256216896</v>
       </c>
       <c r="E26">
-        <v>0.8215999999999997</v>
+        <v>0.9699999999999998</v>
       </c>
       <c r="F26">
-        <v>3.5616</v>
+        <v>3.71</v>
       </c>
       <c r="G26">
         <v>1.15</v>
@@ -3767,28 +3767,28 @@
         <v>3.723</v>
       </c>
       <c r="M26">
-        <v>0.17914848</v>
+        <v>0.186613</v>
       </c>
       <c r="N26">
-        <v>3.54385152</v>
+        <v>3.536387</v>
       </c>
       <c r="O26">
-        <v>0.7087703040000001</v>
+        <v>0.7072774000000001</v>
       </c>
       <c r="P26">
-        <v>2.835081216</v>
+        <v>2.8291096</v>
       </c>
       <c r="Q26">
-        <v>2.842081216</v>
+        <v>2.8361096</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.139583699553614</v>
+        <v>0.1406344973077161</v>
       </c>
       <c r="T26">
-        <v>1.026969949792755</v>
+        <v>1.038476615896875</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.78164436561226</v>
+        <v>19.95037859098776</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3813,22 +3813,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1155358729807871</v>
+        <v>0.1153305343008275</v>
       </c>
       <c r="C27">
-        <v>11.73738256216896</v>
+        <v>11.6067451897416</v>
       </c>
       <c r="D27">
-        <v>14.29738256216896</v>
+        <v>14.3151451897416</v>
       </c>
       <c r="E27">
-        <v>0.9699999999999998</v>
+        <v>1.1184</v>
       </c>
       <c r="F27">
-        <v>3.71</v>
+        <v>3.8584</v>
       </c>
       <c r="G27">
         <v>1.15</v>
@@ -3849,28 +3849,28 @@
         <v>3.723</v>
       </c>
       <c r="M27">
-        <v>0.186613</v>
+        <v>0.19407752</v>
       </c>
       <c r="N27">
-        <v>3.536387</v>
+        <v>3.52892248</v>
       </c>
       <c r="O27">
-        <v>0.7072774000000001</v>
+        <v>0.705784496</v>
       </c>
       <c r="P27">
-        <v>2.8291096</v>
+        <v>2.823137984</v>
       </c>
       <c r="Q27">
-        <v>2.8361096</v>
+        <v>2.830137984</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1406344973077161</v>
+        <v>0.1417136950011182</v>
       </c>
       <c r="T27">
-        <v>1.038476615896875</v>
+        <v>1.050294272976783</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.95037859098776</v>
+        <v>19.18305633748824</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3895,22 +3895,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1153305343008275</v>
+        <v>0.115125195620868</v>
       </c>
       <c r="C28">
-        <v>11.6067451897416</v>
+        <v>11.47615200769741</v>
       </c>
       <c r="D28">
-        <v>14.3151451897416</v>
+        <v>14.33295200769741</v>
       </c>
       <c r="E28">
-        <v>1.1184</v>
+        <v>1.2668</v>
       </c>
       <c r="F28">
-        <v>3.8584</v>
+        <v>4.0068</v>
       </c>
       <c r="G28">
         <v>1.15</v>
@@ -3931,28 +3931,28 @@
         <v>3.723</v>
       </c>
       <c r="M28">
-        <v>0.19407752</v>
+        <v>0.20154204</v>
       </c>
       <c r="N28">
-        <v>3.52892248</v>
+        <v>3.52145796</v>
       </c>
       <c r="O28">
-        <v>0.705784496</v>
+        <v>0.704291592</v>
       </c>
       <c r="P28">
-        <v>2.823137984</v>
+        <v>2.817166368</v>
       </c>
       <c r="Q28">
-        <v>2.830137984</v>
+        <v>2.824166368</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1417136950011182</v>
+        <v>0.1428224597546137</v>
       </c>
       <c r="T28">
-        <v>1.050294272976783</v>
+        <v>1.062435701483537</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.18305633748824</v>
+        <v>18.47257276943311</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3977,22 +3977,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.115125195620868</v>
+        <v>0.1149198569409084</v>
       </c>
       <c r="C29">
-        <v>11.47615200769741</v>
+        <v>11.34560318114897</v>
       </c>
       <c r="D29">
-        <v>14.33295200769741</v>
+        <v>14.35080318114897</v>
       </c>
       <c r="E29">
-        <v>1.2668</v>
+        <v>1.4152</v>
       </c>
       <c r="F29">
-        <v>4.0068</v>
+        <v>4.155200000000001</v>
       </c>
       <c r="G29">
         <v>1.15</v>
@@ -4013,28 +4013,28 @@
         <v>3.723</v>
       </c>
       <c r="M29">
-        <v>0.20154204</v>
+        <v>0.20900656</v>
       </c>
       <c r="N29">
-        <v>3.52145796</v>
+        <v>3.51399344</v>
       </c>
       <c r="O29">
-        <v>0.704291592</v>
+        <v>0.702798688</v>
       </c>
       <c r="P29">
-        <v>2.817166368</v>
+        <v>2.811194752</v>
       </c>
       <c r="Q29">
-        <v>2.824166368</v>
+        <v>2.818194752</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1428224597546137</v>
+        <v>0.1439620235290394</v>
       </c>
       <c r="T29">
-        <v>1.062435701483537</v>
+        <v>1.074914391893257</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.47257276943311</v>
+        <v>17.81283802766765</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4059,22 +4059,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1149198569409084</v>
+        <v>0.1147145182609488</v>
       </c>
       <c r="C30">
-        <v>11.34560318114897</v>
+        <v>11.21509887603246</v>
       </c>
       <c r="D30">
-        <v>14.35080318114897</v>
+        <v>14.36869887603246</v>
       </c>
       <c r="E30">
-        <v>1.4152</v>
+        <v>1.5636</v>
       </c>
       <c r="F30">
-        <v>4.155200000000001</v>
+        <v>4.3036</v>
       </c>
       <c r="G30">
         <v>1.15</v>
@@ -4095,28 +4095,28 @@
         <v>3.723</v>
       </c>
       <c r="M30">
-        <v>0.20900656</v>
+        <v>0.21647108</v>
       </c>
       <c r="N30">
-        <v>3.51399344</v>
+        <v>3.50652892</v>
       </c>
       <c r="O30">
-        <v>0.702798688</v>
+        <v>0.7013057840000001</v>
       </c>
       <c r="P30">
-        <v>2.811194752</v>
+        <v>2.805223136</v>
       </c>
       <c r="Q30">
-        <v>2.818194752</v>
+        <v>2.812223136</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1439620235290394</v>
+        <v>0.1451336876914772</v>
       </c>
       <c r="T30">
-        <v>1.074914391893257</v>
+        <v>1.087744594708884</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.81283802766765</v>
+        <v>17.19860223361014</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4141,22 +4141,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1147145182609488</v>
+        <v>0.1145091795809893</v>
       </c>
       <c r="C31">
-        <v>11.21509887603246</v>
+        <v>11.08463925911276</v>
       </c>
       <c r="D31">
-        <v>14.36869887603246</v>
+        <v>14.38663925911276</v>
       </c>
       <c r="E31">
-        <v>1.563599999999999</v>
+        <v>1.712</v>
       </c>
       <c r="F31">
-        <v>4.303599999999999</v>
+        <v>4.452</v>
       </c>
       <c r="G31">
         <v>1.15</v>
@@ -4177,28 +4177,28 @@
         <v>3.723</v>
       </c>
       <c r="M31">
-        <v>0.21647108</v>
+        <v>0.2239356</v>
       </c>
       <c r="N31">
-        <v>3.50652892</v>
+        <v>3.4990644</v>
       </c>
       <c r="O31">
-        <v>0.7013057840000001</v>
+        <v>0.6998128800000001</v>
       </c>
       <c r="P31">
-        <v>2.805223136</v>
+        <v>2.79925152</v>
       </c>
       <c r="Q31">
-        <v>2.812223136</v>
+        <v>2.80625152</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1451336876914772</v>
+        <v>0.1463388279728419</v>
       </c>
       <c r="T31">
-        <v>1.087744594708884</v>
+        <v>1.100941374747815</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.19860223361015</v>
+        <v>16.6253154924898</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4223,22 +4223,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1145091795809893</v>
+        <v>0.1143038409010297</v>
       </c>
       <c r="C32">
-        <v>11.08463925911276</v>
+        <v>10.95422449798869</v>
       </c>
       <c r="D32">
-        <v>14.38663925911276</v>
+        <v>14.40462449798869</v>
       </c>
       <c r="E32">
-        <v>1.712</v>
+        <v>1.860399999999999</v>
       </c>
       <c r="F32">
-        <v>4.452</v>
+        <v>4.6004</v>
       </c>
       <c r="G32">
         <v>1.15</v>
@@ -4259,28 +4259,28 @@
         <v>3.723</v>
       </c>
       <c r="M32">
-        <v>0.2239356</v>
+        <v>0.23140012</v>
       </c>
       <c r="N32">
-        <v>3.4990644</v>
+        <v>3.49159988</v>
       </c>
       <c r="O32">
-        <v>0.6998128800000001</v>
+        <v>0.6983199760000001</v>
       </c>
       <c r="P32">
-        <v>2.79925152</v>
+        <v>2.793279904</v>
       </c>
       <c r="Q32">
-        <v>2.80625152</v>
+        <v>2.800279904</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1463388279728419</v>
+        <v>0.1475788998565648</v>
       </c>
       <c r="T32">
-        <v>1.100941374747815</v>
+        <v>1.114520670150194</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.6253154924898</v>
+        <v>16.08901499273207</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4305,22 +4305,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1143038409010297</v>
+        <v>0.1140985022210702</v>
       </c>
       <c r="C33">
-        <v>10.95422449798869</v>
+        <v>10.82385476109821</v>
       </c>
       <c r="D33">
-        <v>14.40462449798869</v>
+        <v>14.42265476109821</v>
       </c>
       <c r="E33">
-        <v>1.860399999999999</v>
+        <v>2.0088</v>
       </c>
       <c r="F33">
-        <v>4.6004</v>
+        <v>4.7488</v>
       </c>
       <c r="G33">
         <v>1.15</v>
@@ -4341,28 +4341,28 @@
         <v>3.723</v>
       </c>
       <c r="M33">
-        <v>0.23140012</v>
+        <v>0.23886464</v>
       </c>
       <c r="N33">
-        <v>3.49159988</v>
+        <v>3.48413536</v>
       </c>
       <c r="O33">
-        <v>0.6983199760000001</v>
+        <v>0.696827072</v>
       </c>
       <c r="P33">
-        <v>2.793279904</v>
+        <v>2.787308288</v>
       </c>
       <c r="Q33">
-        <v>2.800279904</v>
+        <v>2.794308288</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1475788998565648</v>
+        <v>0.1488554444427503</v>
       </c>
       <c r="T33">
-        <v>1.114520670150194</v>
+        <v>1.128499356593818</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.08901499273207</v>
+        <v>15.58623327420919</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4387,22 +4387,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1140985022210702</v>
+        <v>0.1138931635411106</v>
       </c>
       <c r="C34">
-        <v>10.82385476109821</v>
+        <v>10.69353021772364</v>
       </c>
       <c r="D34">
-        <v>14.42265476109821</v>
+        <v>14.44073021772364</v>
       </c>
       <c r="E34">
-        <v>2.0088</v>
+        <v>2.1572</v>
       </c>
       <c r="F34">
-        <v>4.7488</v>
+        <v>4.8972</v>
       </c>
       <c r="G34">
         <v>1.15</v>
@@ -4423,28 +4423,28 @@
         <v>3.723</v>
       </c>
       <c r="M34">
-        <v>0.23886464</v>
+        <v>0.24632916</v>
       </c>
       <c r="N34">
-        <v>3.48413536</v>
+        <v>3.47667084</v>
       </c>
       <c r="O34">
-        <v>0.696827072</v>
+        <v>0.695334168</v>
       </c>
       <c r="P34">
-        <v>2.787308288</v>
+        <v>2.781336672</v>
       </c>
       <c r="Q34">
-        <v>2.794308288</v>
+        <v>2.788336672</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1488554444427503</v>
+        <v>0.1501700948374786</v>
       </c>
       <c r="T34">
-        <v>1.128499356593818</v>
+        <v>1.142895317259641</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.58623327420919</v>
+        <v>15.11392317499073</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4469,22 +4469,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1138931635411106</v>
+        <v>0.1136878248611511</v>
       </c>
       <c r="C35">
-        <v>10.69353021772364</v>
+        <v>10.56325103799703</v>
       </c>
       <c r="D35">
-        <v>14.44073021772364</v>
+        <v>14.45885103799703</v>
       </c>
       <c r="E35">
-        <v>2.1572</v>
+        <v>2.3056</v>
       </c>
       <c r="F35">
-        <v>4.8972</v>
+        <v>5.0456</v>
       </c>
       <c r="G35">
         <v>1.15</v>
@@ -4505,28 +4505,28 @@
         <v>3.723</v>
       </c>
       <c r="M35">
-        <v>0.24632916</v>
+        <v>0.25379368</v>
       </c>
       <c r="N35">
-        <v>3.47667084</v>
+        <v>3.46920632</v>
       </c>
       <c r="O35">
-        <v>0.695334168</v>
+        <v>0.693841264</v>
       </c>
       <c r="P35">
-        <v>2.781336672</v>
+        <v>2.775365056</v>
       </c>
       <c r="Q35">
-        <v>2.788336672</v>
+        <v>2.782365056</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1501700948374786</v>
+        <v>0.1515245831229562</v>
       </c>
       <c r="T35">
-        <v>1.142895317259641</v>
+        <v>1.157727519157761</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.11392317499073</v>
+        <v>14.66939602278512</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1136878248611511</v>
+        <v>0.1134824861811915</v>
       </c>
       <c r="C36">
-        <v>10.56325103799703</v>
+        <v>10.43301739290542</v>
       </c>
       <c r="D36">
-        <v>14.45885103799703</v>
+        <v>14.47701739290542</v>
       </c>
       <c r="E36">
-        <v>2.3056</v>
+        <v>2.454000000000001</v>
       </c>
       <c r="F36">
-        <v>5.0456</v>
+        <v>5.194000000000001</v>
       </c>
       <c r="G36">
         <v>1.15</v>
@@ -4587,28 +4587,28 @@
         <v>3.723</v>
       </c>
       <c r="M36">
-        <v>0.25379368</v>
+        <v>0.2612582000000001</v>
       </c>
       <c r="N36">
-        <v>3.46920632</v>
+        <v>3.4617418</v>
       </c>
       <c r="O36">
-        <v>0.693841264</v>
+        <v>0.69234836</v>
       </c>
       <c r="P36">
-        <v>2.775365056</v>
+        <v>2.76939344</v>
       </c>
       <c r="Q36">
-        <v>2.782365056</v>
+        <v>2.77639344</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1515245831229562</v>
+        <v>0.1529207479710639</v>
       </c>
       <c r="T36">
-        <v>1.157727519157761</v>
+        <v>1.1730160964989</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.66939602278512</v>
+        <v>14.25027042213412</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4633,22 +4633,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1134824861811915</v>
+        <v>0.113277147501232</v>
       </c>
       <c r="C37">
-        <v>10.43301739290542</v>
+        <v>10.30282945429628</v>
       </c>
       <c r="D37">
-        <v>14.47701739290542</v>
+        <v>14.49522945429628</v>
       </c>
       <c r="E37">
-        <v>2.454000000000001</v>
+        <v>2.6024</v>
       </c>
       <c r="F37">
-        <v>5.194000000000001</v>
+        <v>5.3424</v>
       </c>
       <c r="G37">
         <v>1.15</v>
@@ -4669,28 +4669,28 @@
         <v>3.723</v>
       </c>
       <c r="M37">
-        <v>0.2612582000000001</v>
+        <v>0.26872272</v>
       </c>
       <c r="N37">
-        <v>3.4617418</v>
+        <v>3.45427728</v>
       </c>
       <c r="O37">
-        <v>0.69234836</v>
+        <v>0.690855456</v>
       </c>
       <c r="P37">
-        <v>2.76939344</v>
+        <v>2.763421824</v>
       </c>
       <c r="Q37">
-        <v>2.77639344</v>
+        <v>2.770421824</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1529207479710639</v>
+        <v>0.154360542970675</v>
       </c>
       <c r="T37">
-        <v>1.1730160964989</v>
+        <v>1.18878244188195</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.25027042213412</v>
+        <v>13.85442957707484</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4715,22 +4715,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.113277147501232</v>
+        <v>0.1130718088212724</v>
       </c>
       <c r="C38">
-        <v>10.30282945429628</v>
+        <v>10.1726873948829</v>
       </c>
       <c r="D38">
-        <v>14.49522945429628</v>
+        <v>14.5134873948829</v>
       </c>
       <c r="E38">
-        <v>2.602399999999999</v>
+        <v>2.7508</v>
       </c>
       <c r="F38">
-        <v>5.3424</v>
+        <v>5.4908</v>
       </c>
       <c r="G38">
         <v>1.15</v>
@@ -4751,28 +4751,28 @@
         <v>3.723</v>
       </c>
       <c r="M38">
-        <v>0.26872272</v>
+        <v>0.27618724</v>
       </c>
       <c r="N38">
-        <v>3.45427728</v>
+        <v>3.44681276</v>
       </c>
       <c r="O38">
-        <v>0.690855456</v>
+        <v>0.689362552</v>
       </c>
       <c r="P38">
-        <v>2.763421824</v>
+        <v>2.757450208</v>
       </c>
       <c r="Q38">
-        <v>2.770421824</v>
+        <v>2.764450208</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.154360542970675</v>
+        <v>0.1558460457480515</v>
       </c>
       <c r="T38">
-        <v>1.188782441881949</v>
+        <v>1.205049306166049</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.85442957707484</v>
+        <v>13.47998553445119</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4797,22 +4797,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1130718088212724</v>
+        <v>0.1128664701413129</v>
       </c>
       <c r="C39">
-        <v>10.1726873948829</v>
+        <v>10.04259138824984</v>
       </c>
       <c r="D39">
-        <v>14.5134873948829</v>
+        <v>14.53179138824984</v>
       </c>
       <c r="E39">
-        <v>2.7508</v>
+        <v>2.8992</v>
       </c>
       <c r="F39">
-        <v>5.4908</v>
+        <v>5.6392</v>
       </c>
       <c r="G39">
         <v>1.15</v>
@@ -4833,28 +4833,28 @@
         <v>3.723</v>
       </c>
       <c r="M39">
-        <v>0.27618724</v>
+        <v>0.28365176</v>
       </c>
       <c r="N39">
-        <v>3.44681276</v>
+        <v>3.43934824</v>
       </c>
       <c r="O39">
-        <v>0.689362552</v>
+        <v>0.6878696479999999</v>
       </c>
       <c r="P39">
-        <v>2.757450208</v>
+        <v>2.751478592</v>
       </c>
       <c r="Q39">
-        <v>2.764450208</v>
+        <v>2.758478592</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1558460457480515</v>
+        <v>0.1573794679698595</v>
       </c>
       <c r="T39">
-        <v>1.205049306166049</v>
+        <v>1.221840908007699</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.47998553445119</v>
+        <v>13.12524907301827</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4879,22 +4879,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1128664701413129</v>
+        <v>0.1131291314613533</v>
       </c>
       <c r="C40">
-        <v>10.04259138824984</v>
+        <v>9.870785855886123</v>
       </c>
       <c r="D40">
-        <v>14.53179138824984</v>
+        <v>14.50838585588612</v>
       </c>
       <c r="E40">
-        <v>2.8992</v>
+        <v>3.0476</v>
       </c>
       <c r="F40">
-        <v>5.6392</v>
+        <v>5.7876</v>
       </c>
       <c r="G40">
         <v>1.15</v>
@@ -4915,45 +4915,45 @@
         <v>3.723</v>
       </c>
       <c r="M40">
-        <v>0.28365176</v>
+        <v>0.29979768</v>
       </c>
       <c r="N40">
-        <v>3.43934824</v>
+        <v>3.42320232</v>
       </c>
       <c r="O40">
-        <v>0.6878696479999999</v>
+        <v>0.684640464</v>
       </c>
       <c r="P40">
-        <v>2.751478592</v>
+        <v>2.738561856</v>
       </c>
       <c r="Q40">
-        <v>2.758478592</v>
+        <v>2.745561856</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1573794679698595</v>
+        <v>0.1589631663300874</v>
       </c>
       <c r="T40">
-        <v>1.221840908007699</v>
+        <v>1.239183054172027</v>
       </c>
       <c r="U40">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y40">
-        <v>13.12524907301827</v>
+        <v>12.41837495206767</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4961,22 +4961,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1131291314613533</v>
+        <v>0.1129357927813938</v>
       </c>
       <c r="C41">
-        <v>9.870785855886123</v>
+        <v>9.739606773085759</v>
       </c>
       <c r="D41">
-        <v>14.50838585588612</v>
+        <v>14.52560677308576</v>
       </c>
       <c r="E41">
-        <v>3.0476</v>
+        <v>3.196</v>
       </c>
       <c r="F41">
-        <v>5.7876</v>
+        <v>5.936</v>
       </c>
       <c r="G41">
         <v>1.15</v>
@@ -4997,28 +4997,28 @@
         <v>3.723</v>
       </c>
       <c r="M41">
-        <v>0.29979768</v>
+        <v>0.3074848</v>
       </c>
       <c r="N41">
-        <v>3.42320232</v>
+        <v>3.4155152</v>
       </c>
       <c r="O41">
-        <v>0.684640464</v>
+        <v>0.68310304</v>
       </c>
       <c r="P41">
-        <v>2.738561856</v>
+        <v>2.73241216</v>
       </c>
       <c r="Q41">
-        <v>2.745561856</v>
+        <v>2.73941216</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1589631663300874</v>
+        <v>0.1605996546356563</v>
       </c>
       <c r="T41">
-        <v>1.239183054172027</v>
+        <v>1.257103271875165</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>12.41837495206767</v>
+        <v>12.10791557826598</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5043,22 +5043,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1129357927813938</v>
+        <v>0.1127424541014342</v>
       </c>
       <c r="C42">
-        <v>9.739606773085759</v>
+        <v>9.608468620050596</v>
       </c>
       <c r="D42">
-        <v>14.52560677308576</v>
+        <v>14.5428686200506</v>
       </c>
       <c r="E42">
-        <v>3.196</v>
+        <v>3.3444</v>
       </c>
       <c r="F42">
-        <v>5.936</v>
+        <v>6.0844</v>
       </c>
       <c r="G42">
         <v>1.15</v>
@@ -5079,28 +5079,28 @@
         <v>3.723</v>
       </c>
       <c r="M42">
-        <v>0.3074848</v>
+        <v>0.31517192</v>
       </c>
       <c r="N42">
-        <v>3.4155152</v>
+        <v>3.40782808</v>
       </c>
       <c r="O42">
-        <v>0.68310304</v>
+        <v>0.681565616</v>
       </c>
       <c r="P42">
-        <v>2.73241216</v>
+        <v>2.726262464</v>
       </c>
       <c r="Q42">
-        <v>2.73941216</v>
+        <v>2.733262464</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1605996546356563</v>
+        <v>0.162291617121075</v>
       </c>
       <c r="T42">
-        <v>1.257103271875165</v>
+        <v>1.27563095458519</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.10791557826598</v>
+        <v>11.81260056416193</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5125,22 +5125,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1127424541014342</v>
+        <v>0.1125491154214747</v>
       </c>
       <c r="C43">
-        <v>9.608468620050596</v>
+        <v>9.47737154287379</v>
       </c>
       <c r="D43">
-        <v>14.5428686200506</v>
+        <v>14.56017154287379</v>
       </c>
       <c r="E43">
-        <v>3.3444</v>
+        <v>3.4928</v>
       </c>
       <c r="F43">
-        <v>6.0844</v>
+        <v>6.2328</v>
       </c>
       <c r="G43">
         <v>1.15</v>
@@ -5161,28 +5161,28 @@
         <v>3.723</v>
       </c>
       <c r="M43">
-        <v>0.31517192</v>
+        <v>0.32285904</v>
       </c>
       <c r="N43">
-        <v>3.40782808</v>
+        <v>3.40014096</v>
       </c>
       <c r="O43">
-        <v>0.681565616</v>
+        <v>0.680028192</v>
       </c>
       <c r="P43">
-        <v>2.726262464</v>
+        <v>2.720112768</v>
       </c>
       <c r="Q43">
-        <v>2.733262464</v>
+        <v>2.727112768</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.162291617121075</v>
+        <v>0.1640419231404736</v>
       </c>
       <c r="T43">
-        <v>1.27563095458519</v>
+        <v>1.294797522905905</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.81260056416193</v>
+        <v>11.53134816977713</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5207,22 +5207,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1125491154214747</v>
+        <v>0.1123557767415151</v>
       </c>
       <c r="C44">
-        <v>9.47737154287379</v>
+        <v>9.346315688344626</v>
       </c>
       <c r="D44">
-        <v>14.56017154287379</v>
+        <v>14.57751568834463</v>
       </c>
       <c r="E44">
-        <v>3.4928</v>
+        <v>3.6412</v>
       </c>
       <c r="F44">
-        <v>6.2328</v>
+        <v>6.3812</v>
       </c>
       <c r="G44">
         <v>1.15</v>
@@ -5243,28 +5243,28 @@
         <v>3.723</v>
       </c>
       <c r="M44">
-        <v>0.32285904</v>
+        <v>0.33054616</v>
       </c>
       <c r="N44">
-        <v>3.40014096</v>
+        <v>3.39245384</v>
       </c>
       <c r="O44">
-        <v>0.680028192</v>
+        <v>0.6784907680000001</v>
       </c>
       <c r="P44">
-        <v>2.720112768</v>
+        <v>2.713963072</v>
       </c>
       <c r="Q44">
-        <v>2.727112768</v>
+        <v>2.720963072</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1640419231404736</v>
+        <v>0.1658536434061669</v>
       </c>
       <c r="T44">
-        <v>1.294797522905905</v>
+        <v>1.314636602395768</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.53134816977713</v>
+        <v>11.26317728210789</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5289,22 +5289,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1123557767415151</v>
+        <v>0.1121624380615556</v>
       </c>
       <c r="C45">
-        <v>9.346315688344626</v>
+        <v>9.215301203952626</v>
       </c>
       <c r="D45">
-        <v>14.57751568834463</v>
+        <v>14.59490120395263</v>
       </c>
       <c r="E45">
-        <v>3.6412</v>
+        <v>3.7896</v>
       </c>
       <c r="F45">
-        <v>6.3812</v>
+        <v>6.5296</v>
       </c>
       <c r="G45">
         <v>1.15</v>
@@ -5325,28 +5325,28 @@
         <v>3.723</v>
       </c>
       <c r="M45">
-        <v>0.33054616</v>
+        <v>0.33823328</v>
       </c>
       <c r="N45">
-        <v>3.39245384</v>
+        <v>3.38476672</v>
       </c>
       <c r="O45">
-        <v>0.6784907680000001</v>
+        <v>0.6769533440000001</v>
       </c>
       <c r="P45">
-        <v>2.713963072</v>
+        <v>2.707813376</v>
       </c>
       <c r="Q45">
-        <v>2.720963072</v>
+        <v>2.714813376</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1658536434061669</v>
+        <v>0.1677300679670635</v>
       </c>
       <c r="T45">
-        <v>1.314636602395768</v>
+        <v>1.33518422043884</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5363,7 +5363,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.26317728210789</v>
+        <v>11.0071959802418</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5371,22 +5371,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1121624380615556</v>
+        <v>0.111969099381596</v>
       </c>
       <c r="C46">
-        <v>9.215301203952626</v>
+        <v>9.084328237891764</v>
       </c>
       <c r="D46">
-        <v>14.59490120395263</v>
+        <v>14.61232823789176</v>
       </c>
       <c r="E46">
-        <v>3.7896</v>
+        <v>3.938</v>
       </c>
       <c r="F46">
-        <v>6.5296</v>
+        <v>6.678</v>
       </c>
       <c r="G46">
         <v>1.15</v>
@@ -5407,28 +5407,28 @@
         <v>3.723</v>
       </c>
       <c r="M46">
-        <v>0.33823328</v>
+        <v>0.3459204</v>
       </c>
       <c r="N46">
-        <v>3.38476672</v>
+        <v>3.3770796</v>
       </c>
       <c r="O46">
-        <v>0.6769533440000001</v>
+        <v>0.6754159200000001</v>
       </c>
       <c r="P46">
-        <v>2.707813376</v>
+        <v>2.70166368</v>
       </c>
       <c r="Q46">
-        <v>2.714813376</v>
+        <v>2.70866368</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1677300679670635</v>
+        <v>0.1696747261483564</v>
       </c>
       <c r="T46">
-        <v>1.33518422043884</v>
+        <v>1.356479024592569</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.0071959802418</v>
+        <v>10.76259162512532</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5453,22 +5453,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.111969099381596</v>
+        <v>0.1117757607016365</v>
       </c>
       <c r="C47">
-        <v>9.084328237891764</v>
+        <v>8.95339693906466</v>
       </c>
       <c r="D47">
-        <v>14.61232823789176</v>
+        <v>14.62979693906466</v>
       </c>
       <c r="E47">
-        <v>3.938</v>
+        <v>4.0864</v>
       </c>
       <c r="F47">
-        <v>6.678</v>
+        <v>6.8264</v>
       </c>
       <c r="G47">
         <v>1.15</v>
@@ -5489,28 +5489,28 @@
         <v>3.723</v>
       </c>
       <c r="M47">
-        <v>0.3459204</v>
+        <v>0.35360752</v>
       </c>
       <c r="N47">
-        <v>3.3770796</v>
+        <v>3.36939248</v>
       </c>
       <c r="O47">
-        <v>0.6754159200000001</v>
+        <v>0.6738784959999999</v>
       </c>
       <c r="P47">
-        <v>2.70166368</v>
+        <v>2.695513984</v>
       </c>
       <c r="Q47">
-        <v>2.70866368</v>
+        <v>2.702513984</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1696747261483564</v>
+        <v>0.1716914087067342</v>
       </c>
       <c r="T47">
-        <v>1.356479024592569</v>
+        <v>1.378562525196437</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.76259162512532</v>
+        <v>10.52862224197042</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5535,22 +5535,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1117757607016365</v>
+        <v>0.1115824220216769</v>
       </c>
       <c r="C48">
-        <v>8.95339693906466</v>
+        <v>8.822507457086825</v>
       </c>
       <c r="D48">
-        <v>14.62979693906466</v>
+        <v>14.64730745708682</v>
       </c>
       <c r="E48">
-        <v>4.0864</v>
+        <v>4.2348</v>
       </c>
       <c r="F48">
-        <v>6.8264</v>
+        <v>6.9748</v>
       </c>
       <c r="G48">
         <v>1.15</v>
@@ -5571,28 +5571,28 @@
         <v>3.723</v>
       </c>
       <c r="M48">
-        <v>0.35360752</v>
+        <v>0.36129464</v>
       </c>
       <c r="N48">
-        <v>3.36939248</v>
+        <v>3.36170536</v>
       </c>
       <c r="O48">
-        <v>0.6738784959999999</v>
+        <v>0.672341072</v>
       </c>
       <c r="P48">
-        <v>2.695513984</v>
+        <v>2.689364288</v>
       </c>
       <c r="Q48">
-        <v>2.702513984</v>
+        <v>2.696364288</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1716914087067342</v>
+        <v>0.17378419249373</v>
       </c>
       <c r="T48">
-        <v>1.378562525196437</v>
+        <v>1.401479365445734</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.52862224197042</v>
+        <v>10.30460900277956</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1115824220216769</v>
+        <v>0.1113890833417174</v>
       </c>
       <c r="C49">
-        <v>8.822507457086825</v>
+        <v>8.691659942290928</v>
       </c>
       <c r="D49">
-        <v>14.64730745708682</v>
+        <v>14.66485994229093</v>
       </c>
       <c r="E49">
-        <v>4.2348</v>
+        <v>4.3832</v>
       </c>
       <c r="F49">
-        <v>6.9748</v>
+        <v>7.123200000000001</v>
       </c>
       <c r="G49">
         <v>1.15</v>
@@ -5653,28 +5653,28 @@
         <v>3.723</v>
       </c>
       <c r="M49">
-        <v>0.36129464</v>
+        <v>0.36898176</v>
       </c>
       <c r="N49">
-        <v>3.36170536</v>
+        <v>3.35401824</v>
       </c>
       <c r="O49">
-        <v>0.672341072</v>
+        <v>0.670803648</v>
       </c>
       <c r="P49">
-        <v>2.689364288</v>
+        <v>2.683214592</v>
       </c>
       <c r="Q49">
-        <v>2.696364288</v>
+        <v>2.690214592</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.17378419249373</v>
+        <v>0.1759574679648411</v>
       </c>
       <c r="T49">
-        <v>1.401479365445734</v>
+        <v>1.425277622627696</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.30460900277956</v>
+        <v>10.08992964855498</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5699,22 +5699,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1113890833417174</v>
+        <v>0.1111957446617578</v>
       </c>
       <c r="C50">
-        <v>8.691659942290929</v>
+        <v>8.560854545731113</v>
       </c>
       <c r="D50">
-        <v>14.66485994229093</v>
+        <v>14.68245454573111</v>
       </c>
       <c r="E50">
-        <v>4.3832</v>
+        <v>4.531599999999999</v>
       </c>
       <c r="F50">
-        <v>7.1232</v>
+        <v>7.271599999999999</v>
       </c>
       <c r="G50">
         <v>1.15</v>
@@ -5735,28 +5735,28 @@
         <v>3.723</v>
       </c>
       <c r="M50">
-        <v>0.36898176</v>
+        <v>0.37666888</v>
       </c>
       <c r="N50">
-        <v>3.35401824</v>
+        <v>3.34633112</v>
       </c>
       <c r="O50">
-        <v>0.670803648</v>
+        <v>0.669266224</v>
       </c>
       <c r="P50">
-        <v>2.683214592</v>
+        <v>2.677064896</v>
       </c>
       <c r="Q50">
-        <v>2.690214592</v>
+        <v>2.684064896</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1759574679648411</v>
+        <v>0.1782159699250153</v>
       </c>
       <c r="T50">
-        <v>1.425277622627696</v>
+        <v>1.450009144797185</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.08992964855499</v>
+        <v>9.884012716951823</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5781,22 +5781,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1111957446617578</v>
+        <v>0.1116824059817983</v>
       </c>
       <c r="C51">
-        <v>8.560854545731113</v>
+        <v>8.368246765557858</v>
       </c>
       <c r="D51">
-        <v>14.68245454573111</v>
+        <v>14.63824676555786</v>
       </c>
       <c r="E51">
-        <v>4.531599999999999</v>
+        <v>4.68</v>
       </c>
       <c r="F51">
-        <v>7.271599999999999</v>
+        <v>7.42</v>
       </c>
       <c r="G51">
         <v>1.15</v>
@@ -5817,45 +5817,45 @@
         <v>3.723</v>
       </c>
       <c r="M51">
-        <v>0.37666888</v>
+        <v>0.39697</v>
       </c>
       <c r="N51">
-        <v>3.34633112</v>
+        <v>3.32603</v>
       </c>
       <c r="O51">
-        <v>0.669266224</v>
+        <v>0.665206</v>
       </c>
       <c r="P51">
-        <v>2.677064896</v>
+        <v>2.660824</v>
       </c>
       <c r="Q51">
-        <v>2.684064896</v>
+        <v>2.667824</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1782159699250153</v>
+        <v>0.1805648119635965</v>
       </c>
       <c r="T51">
-        <v>1.450009144797185</v>
+        <v>1.475729927853455</v>
       </c>
       <c r="U51">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>9.884012716951823</v>
+        <v>9.378542459127894</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5863,22 +5863,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1116824059817983</v>
+        <v>0.1115026673018387</v>
       </c>
       <c r="C52">
-        <v>8.368246765557858</v>
+        <v>8.236142991610699</v>
       </c>
       <c r="D52">
-        <v>14.63824676555786</v>
+        <v>14.6545429916107</v>
       </c>
       <c r="E52">
-        <v>4.68</v>
+        <v>4.8284</v>
       </c>
       <c r="F52">
-        <v>7.42</v>
+        <v>7.5684</v>
       </c>
       <c r="G52">
         <v>1.15</v>
@@ -5899,28 +5899,28 @@
         <v>3.723</v>
       </c>
       <c r="M52">
-        <v>0.39697</v>
+        <v>0.4049094</v>
       </c>
       <c r="N52">
-        <v>3.32603</v>
+        <v>3.3180906</v>
       </c>
       <c r="O52">
-        <v>0.665206</v>
+        <v>0.66361812</v>
       </c>
       <c r="P52">
-        <v>2.660824</v>
+        <v>2.65447248</v>
       </c>
       <c r="Q52">
-        <v>2.667824</v>
+        <v>2.66147248</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1805648119635965</v>
+        <v>0.1830095251057933</v>
       </c>
       <c r="T52">
-        <v>1.475729927853455</v>
+        <v>1.502500538789572</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.378542459127894</v>
+        <v>9.194649469733228</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5945,22 +5945,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1115026673018387</v>
+        <v>0.1113229286218792</v>
       </c>
       <c r="C53">
-        <v>8.236142991610699</v>
+        <v>8.104075542090012</v>
       </c>
       <c r="D53">
-        <v>14.6545429916107</v>
+        <v>14.67087554209001</v>
       </c>
       <c r="E53">
-        <v>4.8284</v>
+        <v>4.9768</v>
       </c>
       <c r="F53">
-        <v>7.5684</v>
+        <v>7.7168</v>
       </c>
       <c r="G53">
         <v>1.15</v>
@@ -5981,28 +5981,28 @@
         <v>3.723</v>
       </c>
       <c r="M53">
-        <v>0.4049094</v>
+        <v>0.4128488</v>
       </c>
       <c r="N53">
-        <v>3.3180906</v>
+        <v>3.3101512</v>
       </c>
       <c r="O53">
-        <v>0.66361812</v>
+        <v>0.66203024</v>
       </c>
       <c r="P53">
-        <v>2.65447248</v>
+        <v>2.64812096</v>
       </c>
       <c r="Q53">
-        <v>2.66147248</v>
+        <v>2.65512096</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1830095251057933</v>
+        <v>0.1855561012955816</v>
       </c>
       <c r="T53">
-        <v>1.502500538789572</v>
+        <v>1.530386591848027</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.194649469733228</v>
+        <v>9.017829287622975</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6027,22 +6027,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1113229286218792</v>
+        <v>0.1111431899419196</v>
       </c>
       <c r="C54">
-        <v>8.104075542090012</v>
+        <v>7.972044538582472</v>
       </c>
       <c r="D54">
-        <v>14.67087554209001</v>
+        <v>14.68724453858247</v>
       </c>
       <c r="E54">
-        <v>4.9768</v>
+        <v>5.1252</v>
       </c>
       <c r="F54">
-        <v>7.7168</v>
+        <v>7.865200000000001</v>
       </c>
       <c r="G54">
         <v>1.15</v>
@@ -6063,28 +6063,28 @@
         <v>3.723</v>
       </c>
       <c r="M54">
-        <v>0.4128488</v>
+        <v>0.4207882</v>
       </c>
       <c r="N54">
-        <v>3.3101512</v>
+        <v>3.3022118</v>
       </c>
       <c r="O54">
-        <v>0.66203024</v>
+        <v>0.66044236</v>
       </c>
       <c r="P54">
-        <v>2.64812096</v>
+        <v>2.64176944</v>
       </c>
       <c r="Q54">
-        <v>2.65512096</v>
+        <v>2.64876944</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1855561012955816</v>
+        <v>0.1882110424296162</v>
       </c>
       <c r="T54">
-        <v>1.530386591848027</v>
+        <v>1.559459285462161</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.017829287622975</v>
+        <v>8.847681565214994</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6109,22 +6109,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1111431899419196</v>
+        <v>0.1109634512619601</v>
       </c>
       <c r="C55">
-        <v>7.972044538582472</v>
+        <v>7.840050103218031</v>
       </c>
       <c r="D55">
-        <v>14.68724453858247</v>
+        <v>14.70365010321803</v>
       </c>
       <c r="E55">
-        <v>5.1252</v>
+        <v>5.2736</v>
       </c>
       <c r="F55">
-        <v>7.865200000000001</v>
+        <v>8.0136</v>
       </c>
       <c r="G55">
         <v>1.15</v>
@@ -6145,28 +6145,28 @@
         <v>3.723</v>
       </c>
       <c r="M55">
-        <v>0.4207882</v>
+        <v>0.4287276</v>
       </c>
       <c r="N55">
-        <v>3.3022118</v>
+        <v>3.2942724</v>
       </c>
       <c r="O55">
-        <v>0.66044236</v>
+        <v>0.65885448</v>
       </c>
       <c r="P55">
-        <v>2.64176944</v>
+        <v>2.63541792</v>
       </c>
       <c r="Q55">
-        <v>2.64876944</v>
+        <v>2.64241792</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1882110424296162</v>
+        <v>0.1909814157868697</v>
       </c>
       <c r="T55">
-        <v>1.559459285462161</v>
+        <v>1.589796009233432</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.847681565214994</v>
+        <v>8.683835610303605</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6191,22 +6191,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1109634512619601</v>
+        <v>0.1107837125820005</v>
       </c>
       <c r="C56">
-        <v>7.840050103218031</v>
+        <v>7.708092358672904</v>
       </c>
       <c r="D56">
-        <v>14.70365010321803</v>
+        <v>14.7200923586729</v>
       </c>
       <c r="E56">
-        <v>5.2736</v>
+        <v>5.422000000000001</v>
       </c>
       <c r="F56">
-        <v>8.0136</v>
+        <v>8.162000000000001</v>
       </c>
       <c r="G56">
         <v>1.15</v>
@@ -6227,28 +6227,28 @@
         <v>3.723</v>
       </c>
       <c r="M56">
-        <v>0.4287276</v>
+        <v>0.436667</v>
       </c>
       <c r="N56">
-        <v>3.2942724</v>
+        <v>3.286333</v>
       </c>
       <c r="O56">
-        <v>0.65885448</v>
+        <v>0.6572666</v>
       </c>
       <c r="P56">
-        <v>2.63541792</v>
+        <v>2.6290664</v>
       </c>
       <c r="Q56">
-        <v>2.64241792</v>
+        <v>2.6360664</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1909814157868697</v>
+        <v>0.19387491684889</v>
       </c>
       <c r="T56">
-        <v>1.589796009233432</v>
+        <v>1.621481031838981</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.683835610303605</v>
+        <v>8.525947690116267</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6273,22 +6273,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1107837125820005</v>
+        <v>0.110603973902041</v>
       </c>
       <c r="C57">
-        <v>7.708092358672904</v>
+        <v>7.57617142817266</v>
       </c>
       <c r="D57">
-        <v>14.7200923586729</v>
+        <v>14.73657142817266</v>
       </c>
       <c r="E57">
-        <v>5.422000000000001</v>
+        <v>5.570400000000001</v>
       </c>
       <c r="F57">
-        <v>8.162000000000001</v>
+        <v>8.310400000000001</v>
       </c>
       <c r="G57">
         <v>1.15</v>
@@ -6309,28 +6309,28 @@
         <v>3.723</v>
       </c>
       <c r="M57">
-        <v>0.436667</v>
+        <v>0.4446064000000001</v>
       </c>
       <c r="N57">
-        <v>3.286333</v>
+        <v>3.2783936</v>
       </c>
       <c r="O57">
-        <v>0.6572666</v>
+        <v>0.65567872</v>
       </c>
       <c r="P57">
-        <v>2.6290664</v>
+        <v>2.62271488</v>
       </c>
       <c r="Q57">
-        <v>2.6360664</v>
+        <v>2.62971488</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.19387491684889</v>
+        <v>0.1968999406864567</v>
       </c>
       <c r="T57">
-        <v>1.621481031838981</v>
+        <v>1.654606282744783</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.525947690116267</v>
+        <v>8.373698624221333</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6355,22 +6355,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.110603973902041</v>
+        <v>0.1104242352220814</v>
       </c>
       <c r="C58">
-        <v>7.57617142817266</v>
+        <v>7.444287435495287</v>
       </c>
       <c r="D58">
-        <v>14.73657142817266</v>
+        <v>14.75308743549529</v>
       </c>
       <c r="E58">
-        <v>5.570400000000001</v>
+        <v>5.7188</v>
       </c>
       <c r="F58">
-        <v>8.310400000000001</v>
+        <v>8.4588</v>
       </c>
       <c r="G58">
         <v>1.15</v>
@@ -6391,28 +6391,28 @@
         <v>3.723</v>
       </c>
       <c r="M58">
-        <v>0.4446064000000001</v>
+        <v>0.4525458</v>
       </c>
       <c r="N58">
-        <v>3.2783936</v>
+        <v>3.2704542</v>
       </c>
       <c r="O58">
-        <v>0.65567872</v>
+        <v>0.65409084</v>
       </c>
       <c r="P58">
-        <v>2.62271488</v>
+        <v>2.61636336</v>
       </c>
       <c r="Q58">
-        <v>2.62971488</v>
+        <v>2.62336336</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1968999406864567</v>
+        <v>0.2000656633071661</v>
       </c>
       <c r="T58">
-        <v>1.654606282744783</v>
+        <v>1.68927224299504</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.373698624221333</v>
+        <v>8.226791630813942</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6437,22 +6437,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1104242352220814</v>
+        <v>0.1102444965421218</v>
       </c>
       <c r="C59">
-        <v>7.444287435495287</v>
+        <v>7.312440504974278</v>
       </c>
       <c r="D59">
-        <v>14.75308743549529</v>
+        <v>14.76964050497428</v>
       </c>
       <c r="E59">
-        <v>5.7188</v>
+        <v>5.8672</v>
       </c>
       <c r="F59">
-        <v>8.4588</v>
+        <v>8.607200000000001</v>
       </c>
       <c r="G59">
         <v>1.15</v>
@@ -6473,28 +6473,28 @@
         <v>3.723</v>
       </c>
       <c r="M59">
-        <v>0.4525458</v>
+        <v>0.4604852</v>
       </c>
       <c r="N59">
-        <v>3.2704542</v>
+        <v>3.2625148</v>
       </c>
       <c r="O59">
-        <v>0.65409084</v>
+        <v>0.6525029600000001</v>
       </c>
       <c r="P59">
-        <v>2.61636336</v>
+        <v>2.61001184</v>
       </c>
       <c r="Q59">
-        <v>2.62336336</v>
+        <v>2.61701184</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2000656633071661</v>
+        <v>0.2033821346240997</v>
       </c>
       <c r="T59">
-        <v>1.68927224299504</v>
+        <v>1.725588963257215</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.226791630813942</v>
+        <v>8.084950395799908</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6519,22 +6519,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1102444965421218</v>
+        <v>0.1100647578621623</v>
       </c>
       <c r="C60">
-        <v>7.31244050497428</v>
+        <v>7.180630761501778</v>
       </c>
       <c r="D60">
-        <v>14.76964050497428</v>
+        <v>14.78623076150178</v>
       </c>
       <c r="E60">
-        <v>5.867199999999999</v>
+        <v>6.015599999999999</v>
       </c>
       <c r="F60">
-        <v>8.607199999999999</v>
+        <v>8.755599999999999</v>
       </c>
       <c r="G60">
         <v>1.15</v>
@@ -6555,28 +6555,28 @@
         <v>3.723</v>
       </c>
       <c r="M60">
-        <v>0.4604851999999999</v>
+        <v>0.4684246</v>
       </c>
       <c r="N60">
-        <v>3.2625148</v>
+        <v>3.2545754</v>
       </c>
       <c r="O60">
-        <v>0.6525029600000001</v>
+        <v>0.65091508</v>
       </c>
       <c r="P60">
-        <v>2.61001184</v>
+        <v>2.60366032</v>
       </c>
       <c r="Q60">
-        <v>2.61701184</v>
+        <v>2.61066032</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2033821346240996</v>
+        <v>0.2068603850296642</v>
       </c>
       <c r="T60">
-        <v>1.725588963257214</v>
+        <v>1.763677230849251</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6593,7 +6593,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.084950395799909</v>
+        <v>7.947917338243978</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6601,22 +6601,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1100647578621623</v>
+        <v>0.1098850191822028</v>
       </c>
       <c r="C61">
-        <v>7.180630761501778</v>
+        <v>7.048858330531713</v>
       </c>
       <c r="D61">
-        <v>14.78623076150178</v>
+        <v>14.80285833053171</v>
       </c>
       <c r="E61">
-        <v>6.015599999999999</v>
+        <v>6.164</v>
       </c>
       <c r="F61">
-        <v>8.755599999999999</v>
+        <v>8.904</v>
       </c>
       <c r="G61">
         <v>1.15</v>
@@ -6637,28 +6637,28 @@
         <v>3.723</v>
       </c>
       <c r="M61">
-        <v>0.4684246</v>
+        <v>0.476364</v>
       </c>
       <c r="N61">
-        <v>3.2545754</v>
+        <v>3.246636</v>
       </c>
       <c r="O61">
-        <v>0.65091508</v>
+        <v>0.6493272</v>
       </c>
       <c r="P61">
-        <v>2.60366032</v>
+        <v>2.5973088</v>
       </c>
       <c r="Q61">
-        <v>2.61066032</v>
+        <v>2.6043088</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2068603850296642</v>
+        <v>0.2105125479555069</v>
       </c>
       <c r="T61">
-        <v>1.763677230849251</v>
+        <v>1.803669911820889</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.947917338243978</v>
+        <v>7.815452049273244</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1098850191822028</v>
+        <v>0.1097052805022432</v>
       </c>
       <c r="C62">
-        <v>7.048858330531713</v>
+        <v>6.917123338082948</v>
       </c>
       <c r="D62">
-        <v>14.80285833053171</v>
+        <v>14.81952333808295</v>
       </c>
       <c r="E62">
-        <v>6.164</v>
+        <v>6.3124</v>
       </c>
       <c r="F62">
-        <v>8.904</v>
+        <v>9.0524</v>
       </c>
       <c r="G62">
         <v>1.15</v>
@@ -6719,28 +6719,28 @@
         <v>3.723</v>
       </c>
       <c r="M62">
-        <v>0.476364</v>
+        <v>0.4843034</v>
       </c>
       <c r="N62">
-        <v>3.246636</v>
+        <v>3.2386966</v>
       </c>
       <c r="O62">
-        <v>0.6493272</v>
+        <v>0.64773932</v>
       </c>
       <c r="P62">
-        <v>2.5973088</v>
+        <v>2.59095728</v>
       </c>
       <c r="Q62">
-        <v>2.6043088</v>
+        <v>2.59795728</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2105125479555069</v>
+        <v>0.2143520012878031</v>
       </c>
       <c r="T62">
-        <v>1.803669911820889</v>
+        <v>1.845713499509022</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.815452049273244</v>
+        <v>7.68732988453106</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6765,22 +6765,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1097052805022432</v>
+        <v>0.1099223418222837</v>
       </c>
       <c r="C63">
-        <v>6.917123338082948</v>
+        <v>6.748602549058694</v>
       </c>
       <c r="D63">
-        <v>14.81952333808295</v>
+        <v>14.79940254905869</v>
       </c>
       <c r="E63">
-        <v>6.3124</v>
+        <v>6.460799999999999</v>
       </c>
       <c r="F63">
-        <v>9.0524</v>
+        <v>9.200799999999999</v>
       </c>
       <c r="G63">
         <v>1.15</v>
@@ -6801,45 +6801,45 @@
         <v>3.723</v>
       </c>
       <c r="M63">
-        <v>0.4843034</v>
+        <v>0.49960344</v>
       </c>
       <c r="N63">
-        <v>3.2386966</v>
+        <v>3.22339656</v>
       </c>
       <c r="O63">
-        <v>0.64773932</v>
+        <v>0.6446793120000001</v>
       </c>
       <c r="P63">
-        <v>2.59095728</v>
+        <v>2.578717248</v>
       </c>
       <c r="Q63">
-        <v>2.59795728</v>
+        <v>2.585717248</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2143520012878031</v>
+        <v>0.2183935311112728</v>
       </c>
       <c r="T63">
-        <v>1.845713499509022</v>
+        <v>1.889969907601793</v>
       </c>
       <c r="U63">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V63">
         <v>0.2</v>
       </c>
       <c r="W63">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y63">
-        <v>7.68732988453106</v>
+        <v>7.45191025906467</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6847,22 +6847,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1099223418222837</v>
+        <v>0.1097490031423241</v>
       </c>
       <c r="C64">
-        <v>6.748602549058694</v>
+        <v>6.616266010452785</v>
       </c>
       <c r="D64">
-        <v>14.79940254905869</v>
+        <v>14.81546601045278</v>
       </c>
       <c r="E64">
-        <v>6.460799999999999</v>
+        <v>6.6092</v>
       </c>
       <c r="F64">
-        <v>9.200799999999999</v>
+        <v>9.3492</v>
       </c>
       <c r="G64">
         <v>1.15</v>
@@ -6883,28 +6883,28 @@
         <v>3.723</v>
       </c>
       <c r="M64">
-        <v>0.49960344</v>
+        <v>0.50766156</v>
       </c>
       <c r="N64">
-        <v>3.22339656</v>
+        <v>3.21533844</v>
       </c>
       <c r="O64">
-        <v>0.6446793120000001</v>
+        <v>0.643067688</v>
       </c>
       <c r="P64">
-        <v>2.578717248</v>
+        <v>2.572270752</v>
       </c>
       <c r="Q64">
-        <v>2.585717248</v>
+        <v>2.579270752</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2183935311112728</v>
+        <v>0.2226535220062814</v>
       </c>
       <c r="T64">
-        <v>1.889969907601793</v>
+        <v>1.936618553969849</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.45191025906467</v>
+        <v>7.333625969238247</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6929,22 +6929,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1097490031423241</v>
+        <v>0.1095756644623646</v>
       </c>
       <c r="C65">
-        <v>6.616266010452785</v>
+        <v>6.483964380711571</v>
       </c>
       <c r="D65">
-        <v>14.81546601045278</v>
+        <v>14.83156438071157</v>
       </c>
       <c r="E65">
-        <v>6.6092</v>
+        <v>6.7576</v>
       </c>
       <c r="F65">
-        <v>9.3492</v>
+        <v>9.4976</v>
       </c>
       <c r="G65">
         <v>1.15</v>
@@ -6965,28 +6965,28 @@
         <v>3.723</v>
       </c>
       <c r="M65">
-        <v>0.50766156</v>
+        <v>0.51571968</v>
       </c>
       <c r="N65">
-        <v>3.21533844</v>
+        <v>3.20728032</v>
       </c>
       <c r="O65">
-        <v>0.643067688</v>
+        <v>0.641456064</v>
       </c>
       <c r="P65">
-        <v>2.572270752</v>
+        <v>2.565824256</v>
       </c>
       <c r="Q65">
-        <v>2.579270752</v>
+        <v>2.572824256</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2226535220062814</v>
+        <v>0.2271501790621238</v>
       </c>
       <c r="T65">
-        <v>1.936618553969849</v>
+        <v>1.985858791802797</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.333625969238247</v>
+        <v>7.219038063468898</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7011,22 +7011,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1095756644623646</v>
+        <v>0.109402325782405</v>
       </c>
       <c r="C66">
-        <v>6.483964380711571</v>
+        <v>6.351697773753937</v>
       </c>
       <c r="D66">
-        <v>14.83156438071157</v>
+        <v>14.84769777375394</v>
       </c>
       <c r="E66">
-        <v>6.7576</v>
+        <v>6.906000000000001</v>
       </c>
       <c r="F66">
-        <v>9.4976</v>
+        <v>9.646000000000001</v>
       </c>
       <c r="G66">
         <v>1.15</v>
@@ -7047,28 +7047,28 @@
         <v>3.723</v>
       </c>
       <c r="M66">
-        <v>0.51571968</v>
+        <v>0.5237778000000001</v>
       </c>
       <c r="N66">
-        <v>3.20728032</v>
+        <v>3.1992222</v>
       </c>
       <c r="O66">
-        <v>0.641456064</v>
+        <v>0.6398444400000001</v>
       </c>
       <c r="P66">
-        <v>2.565824256</v>
+        <v>2.55937776</v>
       </c>
       <c r="Q66">
-        <v>2.572824256</v>
+        <v>2.56637776</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2271501790621238</v>
+        <v>0.2319037879497285</v>
       </c>
       <c r="T66">
-        <v>1.985858791802797</v>
+        <v>2.037912757511914</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.219038063468898</v>
+        <v>7.10797593941553</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7093,22 +7093,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.109402325782405</v>
+        <v>0.1092289871024454</v>
       </c>
       <c r="C67">
-        <v>6.351697773753937</v>
+        <v>6.219466303994984</v>
       </c>
       <c r="D67">
-        <v>14.84769777375394</v>
+        <v>14.86386630399498</v>
       </c>
       <c r="E67">
-        <v>6.906000000000001</v>
+        <v>7.054399999999999</v>
       </c>
       <c r="F67">
-        <v>9.646000000000001</v>
+        <v>9.7944</v>
       </c>
       <c r="G67">
         <v>1.15</v>
@@ -7129,28 +7129,28 @@
         <v>3.723</v>
       </c>
       <c r="M67">
-        <v>0.5237778000000001</v>
+        <v>0.53183592</v>
       </c>
       <c r="N67">
-        <v>3.1992222</v>
+        <v>3.19116408</v>
       </c>
       <c r="O67">
-        <v>0.6398444400000001</v>
+        <v>0.638232816</v>
       </c>
       <c r="P67">
-        <v>2.55937776</v>
+        <v>2.552931264</v>
       </c>
       <c r="Q67">
-        <v>2.56637776</v>
+        <v>2.559931264</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2319037879497285</v>
+        <v>0.2369370208895454</v>
       </c>
       <c r="T67">
-        <v>2.037912757511914</v>
+        <v>2.09302872120392</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.10797593941553</v>
+        <v>7.000279334272872</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7175,22 +7175,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1092289871024454</v>
+        <v>0.1090556484224859</v>
       </c>
       <c r="C68">
-        <v>6.219466303994984</v>
+        <v>6.087270086348719</v>
       </c>
       <c r="D68">
-        <v>14.86386630399498</v>
+        <v>14.88007008634872</v>
       </c>
       <c r="E68">
-        <v>7.054399999999999</v>
+        <v>7.2028</v>
       </c>
       <c r="F68">
-        <v>9.7944</v>
+        <v>9.9428</v>
       </c>
       <c r="G68">
         <v>1.15</v>
@@ -7211,28 +7211,28 @@
         <v>3.723</v>
       </c>
       <c r="M68">
-        <v>0.53183592</v>
+        <v>0.53989404</v>
       </c>
       <c r="N68">
-        <v>3.19116408</v>
+        <v>3.18310596</v>
       </c>
       <c r="O68">
-        <v>0.638232816</v>
+        <v>0.636621192</v>
       </c>
       <c r="P68">
-        <v>2.552931264</v>
+        <v>2.546484768</v>
       </c>
       <c r="Q68">
-        <v>2.559931264</v>
+        <v>2.553484768</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2369370208895454</v>
+        <v>0.2422752982499573</v>
       </c>
       <c r="T68">
-        <v>2.09302872120392</v>
+        <v>2.151485046331805</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.000279334272872</v>
+        <v>6.895797553164321</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7257,22 +7257,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1090556484224859</v>
+        <v>0.1088823097425263</v>
       </c>
       <c r="C69">
-        <v>6.087270086348719</v>
+        <v>5.955109236230808</v>
       </c>
       <c r="D69">
-        <v>14.88007008634872</v>
+        <v>14.89630923623081</v>
       </c>
       <c r="E69">
-        <v>7.2028</v>
+        <v>7.3512</v>
       </c>
       <c r="F69">
-        <v>9.9428</v>
+        <v>10.0912</v>
       </c>
       <c r="G69">
         <v>1.15</v>
@@ -7293,28 +7293,28 @@
         <v>3.723</v>
       </c>
       <c r="M69">
-        <v>0.53989404</v>
+        <v>0.54795216</v>
       </c>
       <c r="N69">
-        <v>3.18310596</v>
+        <v>3.17504784</v>
       </c>
       <c r="O69">
-        <v>0.636621192</v>
+        <v>0.6350095680000001</v>
       </c>
       <c r="P69">
-        <v>2.546484768</v>
+        <v>2.540038272</v>
       </c>
       <c r="Q69">
-        <v>2.553484768</v>
+        <v>2.547038272</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2422752982499573</v>
+        <v>0.2479472179453948</v>
       </c>
       <c r="T69">
-        <v>2.151485046331805</v>
+        <v>2.213594891780182</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -7331,7 +7331,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.895797553164321</v>
+        <v>6.794388765617787</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7339,22 +7339,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1088823097425263</v>
+        <v>0.1087089710625668</v>
       </c>
       <c r="C70">
-        <v>5.955109236230808</v>
+        <v>5.822983869561272</v>
       </c>
       <c r="D70">
-        <v>14.89630923623081</v>
+        <v>14.91258386956127</v>
       </c>
       <c r="E70">
-        <v>7.3512</v>
+        <v>7.499600000000001</v>
       </c>
       <c r="F70">
-        <v>10.0912</v>
+        <v>10.2396</v>
       </c>
       <c r="G70">
         <v>1.15</v>
@@ -7375,28 +7375,28 @@
         <v>3.723</v>
       </c>
       <c r="M70">
-        <v>0.54795216</v>
+        <v>0.5560102800000001</v>
       </c>
       <c r="N70">
-        <v>3.17504784</v>
+        <v>3.16698972</v>
       </c>
       <c r="O70">
-        <v>0.6350095680000001</v>
+        <v>0.6333979439999999</v>
       </c>
       <c r="P70">
-        <v>2.540038272</v>
+        <v>2.533591776</v>
       </c>
       <c r="Q70">
-        <v>2.547038272</v>
+        <v>2.540591776</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2479472179453948</v>
+        <v>0.2539850679437639</v>
       </c>
       <c r="T70">
-        <v>2.213594891780182</v>
+        <v>2.279711824031681</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.794388765617787</v>
+        <v>6.695919363217528</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7421,22 +7421,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1087089710625668</v>
+        <v>0.1085356323826072</v>
       </c>
       <c r="C71">
-        <v>5.822983869561272</v>
+        <v>5.690894102767292</v>
       </c>
       <c r="D71">
-        <v>14.91258386956127</v>
+        <v>14.92889410276729</v>
       </c>
       <c r="E71">
-        <v>7.499600000000001</v>
+        <v>7.648000000000001</v>
       </c>
       <c r="F71">
-        <v>10.2396</v>
+        <v>10.388</v>
       </c>
       <c r="G71">
         <v>1.15</v>
@@ -7457,28 +7457,28 @@
         <v>3.723</v>
       </c>
       <c r="M71">
-        <v>0.5560102800000001</v>
+        <v>0.5640684000000001</v>
       </c>
       <c r="N71">
-        <v>3.16698972</v>
+        <v>3.1589316</v>
       </c>
       <c r="O71">
-        <v>0.6333979439999999</v>
+        <v>0.63178632</v>
       </c>
       <c r="P71">
-        <v>2.533591776</v>
+        <v>2.52714528</v>
       </c>
       <c r="Q71">
-        <v>2.540591776</v>
+        <v>2.53414528</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2539850679437639</v>
+        <v>0.2604254412753574</v>
       </c>
       <c r="T71">
-        <v>2.279711824031681</v>
+        <v>2.350236551766613</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.695919363217528</v>
+        <v>6.60026337231442</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7503,22 +7503,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1085356323826072</v>
+        <v>0.1083622937026477</v>
       </c>
       <c r="C72">
-        <v>5.690894102767292</v>
+        <v>5.55884005278595</v>
       </c>
       <c r="D72">
-        <v>14.92889410276729</v>
+        <v>14.94524005278595</v>
       </c>
       <c r="E72">
-        <v>7.648000000000001</v>
+        <v>7.7964</v>
       </c>
       <c r="F72">
-        <v>10.388</v>
+        <v>10.5364</v>
       </c>
       <c r="G72">
         <v>1.15</v>
@@ -7539,28 +7539,28 @@
         <v>3.723</v>
       </c>
       <c r="M72">
-        <v>0.5640684000000001</v>
+        <v>0.5721265200000001</v>
       </c>
       <c r="N72">
-        <v>3.1589316</v>
+        <v>3.15087348</v>
       </c>
       <c r="O72">
-        <v>0.63178632</v>
+        <v>0.630174696</v>
       </c>
       <c r="P72">
-        <v>2.52714528</v>
+        <v>2.520698783999999</v>
       </c>
       <c r="Q72">
-        <v>2.53414528</v>
+        <v>2.527698784</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2604254412753574</v>
+        <v>0.2673099782849921</v>
       </c>
       <c r="T72">
-        <v>2.350236551766613</v>
+        <v>2.425625053828093</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.60026337231442</v>
+        <v>6.507301916366329</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7585,22 +7585,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1083622937026477</v>
+        <v>0.1081889550226881</v>
       </c>
       <c r="C73">
-        <v>5.558840052785952</v>
+        <v>5.426821837067042</v>
       </c>
       <c r="D73">
-        <v>14.94524005278595</v>
+        <v>14.96162183706704</v>
       </c>
       <c r="E73">
-        <v>7.796399999999998</v>
+        <v>7.944799999999999</v>
       </c>
       <c r="F73">
-        <v>10.5364</v>
+        <v>10.6848</v>
       </c>
       <c r="G73">
         <v>1.15</v>
@@ -7621,28 +7621,28 @@
         <v>3.723</v>
       </c>
       <c r="M73">
-        <v>0.57212652</v>
+        <v>0.5801846399999999</v>
       </c>
       <c r="N73">
-        <v>3.15087348</v>
+        <v>3.14281536</v>
       </c>
       <c r="O73">
-        <v>0.6301746960000001</v>
+        <v>0.6285630720000001</v>
       </c>
       <c r="P73">
-        <v>2.520698784</v>
+        <v>2.514252288</v>
       </c>
       <c r="Q73">
-        <v>2.527698784</v>
+        <v>2.521252288</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.267309978284992</v>
+        <v>0.2746862679381719</v>
       </c>
       <c r="T73">
-        <v>2.425625053828092</v>
+        <v>2.506398448893962</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7659,7 +7659,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.507301916366331</v>
+        <v>6.416922723083466</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7667,22 +7667,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1081889550226881</v>
+        <v>0.1080156163427286</v>
       </c>
       <c r="C74">
-        <v>5.426821837067042</v>
+        <v>5.294839573575876</v>
       </c>
       <c r="D74">
-        <v>14.96162183706704</v>
+        <v>14.97803957357588</v>
       </c>
       <c r="E74">
-        <v>7.944799999999999</v>
+        <v>8.0932</v>
       </c>
       <c r="F74">
-        <v>10.6848</v>
+        <v>10.8332</v>
       </c>
       <c r="G74">
         <v>1.15</v>
@@ -7703,28 +7703,28 @@
         <v>3.723</v>
       </c>
       <c r="M74">
-        <v>0.5801846399999999</v>
+        <v>0.58824276</v>
       </c>
       <c r="N74">
-        <v>3.14281536</v>
+        <v>3.13475724</v>
       </c>
       <c r="O74">
-        <v>0.6285630720000001</v>
+        <v>0.626951448</v>
       </c>
       <c r="P74">
-        <v>2.514252288</v>
+        <v>2.507805792</v>
       </c>
       <c r="Q74">
-        <v>2.521252288</v>
+        <v>2.514805792</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2746862679381719</v>
+        <v>0.2826089494175132</v>
       </c>
       <c r="T74">
-        <v>2.506398448893962</v>
+        <v>2.593155058409156</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.416922723083466</v>
+        <v>6.329019672082322</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7749,22 +7749,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1080156163427286</v>
+        <v>0.107842277662769</v>
       </c>
       <c r="C75">
-        <v>5.294839573575876</v>
+        <v>5.162893380796127</v>
       </c>
       <c r="D75">
-        <v>14.97803957357588</v>
+        <v>14.99449338079613</v>
       </c>
       <c r="E75">
-        <v>8.0932</v>
+        <v>8.2416</v>
       </c>
       <c r="F75">
-        <v>10.8332</v>
+        <v>10.9816</v>
       </c>
       <c r="G75">
         <v>1.15</v>
@@ -7785,28 +7785,28 @@
         <v>3.723</v>
       </c>
       <c r="M75">
-        <v>0.58824276</v>
+        <v>0.59630088</v>
       </c>
       <c r="N75">
-        <v>3.13475724</v>
+        <v>3.12669912</v>
       </c>
       <c r="O75">
-        <v>0.626951448</v>
+        <v>0.625339824</v>
       </c>
       <c r="P75">
-        <v>2.507805792</v>
+        <v>2.501359296</v>
       </c>
       <c r="Q75">
-        <v>2.514805792</v>
+        <v>2.508359296</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2826089494175132</v>
+        <v>0.291141067933727</v>
       </c>
       <c r="T75">
-        <v>2.593155058409156</v>
+        <v>2.686585253271674</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.329019672082322</v>
+        <v>6.243492379216343</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7831,22 +7831,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.107842277662769</v>
+        <v>0.1076689389828095</v>
       </c>
       <c r="C76">
-        <v>5.162893380796127</v>
+        <v>5.030983377732664</v>
       </c>
       <c r="D76">
-        <v>14.99449338079613</v>
+        <v>15.01098337773266</v>
       </c>
       <c r="E76">
-        <v>8.2416</v>
+        <v>8.389999999999999</v>
       </c>
       <c r="F76">
-        <v>10.9816</v>
+        <v>11.13</v>
       </c>
       <c r="G76">
         <v>1.15</v>
@@ -7867,28 +7867,28 @@
         <v>3.723</v>
       </c>
       <c r="M76">
-        <v>0.59630088</v>
+        <v>0.604359</v>
       </c>
       <c r="N76">
-        <v>3.12669912</v>
+        <v>3.118641</v>
       </c>
       <c r="O76">
-        <v>0.625339824</v>
+        <v>0.6237282</v>
       </c>
       <c r="P76">
-        <v>2.501359296</v>
+        <v>2.4949128</v>
       </c>
       <c r="Q76">
-        <v>2.508359296</v>
+        <v>2.5019128</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.291141067933727</v>
+        <v>0.3003557559312379</v>
       </c>
       <c r="T76">
-        <v>2.686585253271674</v>
+        <v>2.787489863723192</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.243492379216343</v>
+        <v>6.160245814160127</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7913,22 +7913,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1076689389828095</v>
+        <v>0.1081036003028499</v>
       </c>
       <c r="C77">
-        <v>5.030983377732664</v>
+        <v>4.841301691003631</v>
       </c>
       <c r="D77">
-        <v>15.01098337773266</v>
+        <v>14.96970169100363</v>
       </c>
       <c r="E77">
-        <v>8.389999999999999</v>
+        <v>8.538399999999999</v>
       </c>
       <c r="F77">
-        <v>11.13</v>
+        <v>11.2784</v>
       </c>
       <c r="G77">
         <v>1.15</v>
@@ -7949,45 +7949,45 @@
         <v>3.723</v>
       </c>
       <c r="M77">
-        <v>0.604359</v>
+        <v>0.6236955199999999</v>
       </c>
       <c r="N77">
-        <v>3.118641</v>
+        <v>3.09930448</v>
       </c>
       <c r="O77">
-        <v>0.6237282</v>
+        <v>0.6198608960000001</v>
       </c>
       <c r="P77">
-        <v>2.4949128</v>
+        <v>2.479443584</v>
       </c>
       <c r="Q77">
-        <v>2.5019128</v>
+        <v>2.486443584</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3003557559312379</v>
+        <v>0.310338334595208</v>
       </c>
       <c r="T77">
-        <v>2.787489863723192</v>
+        <v>2.896803191712337</v>
       </c>
       <c r="U77">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V77">
         <v>0.2</v>
       </c>
       <c r="W77">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>6.160245814160127</v>
+        <v>5.969258846047187</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7995,22 +7995,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1081036003028499</v>
+        <v>0.1079382616228904</v>
       </c>
       <c r="C78">
-        <v>4.841301691003631</v>
+        <v>4.708577842752838</v>
       </c>
       <c r="D78">
-        <v>14.96970169100363</v>
+        <v>14.98537784275284</v>
       </c>
       <c r="E78">
-        <v>8.538399999999999</v>
+        <v>8.6868</v>
       </c>
       <c r="F78">
-        <v>11.2784</v>
+        <v>11.4268</v>
       </c>
       <c r="G78">
         <v>1.15</v>
@@ -8031,28 +8031,28 @@
         <v>3.723</v>
       </c>
       <c r="M78">
-        <v>0.6236955199999999</v>
+        <v>0.6319020400000001</v>
       </c>
       <c r="N78">
-        <v>3.09930448</v>
+        <v>3.09109796</v>
       </c>
       <c r="O78">
-        <v>0.6198608960000001</v>
+        <v>0.618219592</v>
       </c>
       <c r="P78">
-        <v>2.479443584</v>
+        <v>2.472878368</v>
       </c>
       <c r="Q78">
-        <v>2.486443584</v>
+        <v>2.479878368</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.310338334595208</v>
+        <v>0.3211889635777843</v>
       </c>
       <c r="T78">
-        <v>2.896803191712337</v>
+        <v>3.015622026483147</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.969258846047187</v>
+        <v>5.891736003890729</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8077,22 +8077,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1079382616228904</v>
+        <v>0.1077729229429308</v>
       </c>
       <c r="C79">
-        <v>4.708577842752838</v>
+        <v>4.575886860800553</v>
       </c>
       <c r="D79">
-        <v>14.98537784275284</v>
+        <v>15.00108686080056</v>
       </c>
       <c r="E79">
-        <v>8.6868</v>
+        <v>8.8352</v>
       </c>
       <c r="F79">
-        <v>11.4268</v>
+        <v>11.5752</v>
       </c>
       <c r="G79">
         <v>1.15</v>
@@ -8113,28 +8113,28 @@
         <v>3.723</v>
       </c>
       <c r="M79">
-        <v>0.6319020400000001</v>
+        <v>0.64010856</v>
       </c>
       <c r="N79">
-        <v>3.09109796</v>
+        <v>3.08289144</v>
       </c>
       <c r="O79">
-        <v>0.618219592</v>
+        <v>0.616578288</v>
       </c>
       <c r="P79">
-        <v>2.472878368</v>
+        <v>2.466313152</v>
       </c>
       <c r="Q79">
-        <v>2.479878368</v>
+        <v>2.473313152</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3211889635777843</v>
+        <v>0.3330260133769583</v>
       </c>
       <c r="T79">
-        <v>3.015622026483147</v>
+        <v>3.145242573505848</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.891736003890729</v>
+        <v>5.816200926917771</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8159,22 +8159,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1077729229429308</v>
+        <v>0.1076075842629713</v>
       </c>
       <c r="C80">
-        <v>4.575886860800553</v>
+        <v>4.443228848615458</v>
       </c>
       <c r="D80">
-        <v>15.00108686080056</v>
+        <v>15.01682884861546</v>
       </c>
       <c r="E80">
-        <v>8.8352</v>
+        <v>8.983600000000001</v>
       </c>
       <c r="F80">
-        <v>11.5752</v>
+        <v>11.7236</v>
       </c>
       <c r="G80">
         <v>1.15</v>
@@ -8195,28 +8195,28 @@
         <v>3.723</v>
       </c>
       <c r="M80">
-        <v>0.64010856</v>
+        <v>0.64831508</v>
       </c>
       <c r="N80">
-        <v>3.08289144</v>
+        <v>3.07468492</v>
       </c>
       <c r="O80">
-        <v>0.616578288</v>
+        <v>0.614936984</v>
       </c>
       <c r="P80">
-        <v>2.466313152</v>
+        <v>2.459747936</v>
       </c>
       <c r="Q80">
-        <v>2.473313152</v>
+        <v>2.466747936</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3330260133769583</v>
+        <v>0.3459904012522442</v>
       </c>
       <c r="T80">
-        <v>3.145242573505848</v>
+        <v>3.287207934530712</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -8233,7 +8233,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.816200926917771</v>
+        <v>5.742578130374508</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8241,22 +8241,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1076075842629713</v>
+        <v>0.1074422455830117</v>
       </c>
       <c r="C81">
-        <v>4.443228848615458</v>
+        <v>4.310603910101005</v>
       </c>
       <c r="D81">
-        <v>15.01682884861546</v>
+        <v>15.03260391010101</v>
       </c>
       <c r="E81">
-        <v>8.983600000000001</v>
+        <v>9.132</v>
       </c>
       <c r="F81">
-        <v>11.7236</v>
+        <v>11.872</v>
       </c>
       <c r="G81">
         <v>1.15</v>
@@ -8277,28 +8277,28 @@
         <v>3.723</v>
       </c>
       <c r="M81">
-        <v>0.64831508</v>
+        <v>0.6565216</v>
       </c>
       <c r="N81">
-        <v>3.07468492</v>
+        <v>3.0664784</v>
       </c>
       <c r="O81">
-        <v>0.614936984</v>
+        <v>0.61329568</v>
       </c>
       <c r="P81">
-        <v>2.459747936</v>
+        <v>2.45318272</v>
       </c>
       <c r="Q81">
-        <v>2.466747936</v>
+        <v>2.46018272</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3459904012522442</v>
+        <v>0.3602512279150586</v>
       </c>
       <c r="T81">
-        <v>3.287207934530712</v>
+        <v>3.443369831658062</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.742578130374508</v>
+        <v>5.670795903744827</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8323,22 +8323,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1074422455830117</v>
+        <v>0.1072769069030522</v>
       </c>
       <c r="C82">
-        <v>4.310603910101005</v>
+        <v>4.178012149597693</v>
       </c>
       <c r="D82">
-        <v>15.03260391010101</v>
+        <v>15.0484121495977</v>
       </c>
       <c r="E82">
-        <v>9.132</v>
+        <v>9.2804</v>
       </c>
       <c r="F82">
-        <v>11.872</v>
+        <v>12.0204</v>
       </c>
       <c r="G82">
         <v>1.15</v>
@@ -8359,28 +8359,28 @@
         <v>3.723</v>
       </c>
       <c r="M82">
-        <v>0.6565216</v>
+        <v>0.66472812</v>
       </c>
       <c r="N82">
-        <v>3.0664784</v>
+        <v>3.05827188</v>
       </c>
       <c r="O82">
-        <v>0.61329568</v>
+        <v>0.6116543760000001</v>
       </c>
       <c r="P82">
-        <v>2.45318272</v>
+        <v>2.446617504</v>
       </c>
       <c r="Q82">
-        <v>2.46018272</v>
+        <v>2.453617504</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3602512279150586</v>
+        <v>0.3760131942265905</v>
       </c>
       <c r="T82">
-        <v>3.443369831658062</v>
+        <v>3.61596982321987</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.670795903744827</v>
+        <v>5.600786077772669</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8405,22 +8405,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1072769069030522</v>
+        <v>0.1071115682230926</v>
       </c>
       <c r="C83">
-        <v>4.178012149597693</v>
+        <v>4.045453671885394</v>
       </c>
       <c r="D83">
-        <v>15.0484121495977</v>
+        <v>15.0642536718854</v>
       </c>
       <c r="E83">
-        <v>9.2804</v>
+        <v>9.428800000000001</v>
       </c>
       <c r="F83">
-        <v>12.0204</v>
+        <v>12.1688</v>
       </c>
       <c r="G83">
         <v>1.15</v>
@@ -8441,28 +8441,28 @@
         <v>3.723</v>
       </c>
       <c r="M83">
-        <v>0.66472812</v>
+        <v>0.67293464</v>
       </c>
       <c r="N83">
-        <v>3.05827188</v>
+        <v>3.05006536</v>
       </c>
       <c r="O83">
-        <v>0.6116543760000001</v>
+        <v>0.610013072</v>
       </c>
       <c r="P83">
-        <v>2.446617504</v>
+        <v>2.440052288</v>
       </c>
       <c r="Q83">
-        <v>2.453617504</v>
+        <v>2.447052288</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3760131942265905</v>
+        <v>0.3935264901282924</v>
       </c>
       <c r="T83">
-        <v>3.61596982321987</v>
+        <v>3.807747591621878</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.600786077772669</v>
+        <v>5.532483808531538</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8487,22 +8487,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1071115682230926</v>
+        <v>0.1069462295431331</v>
       </c>
       <c r="C84">
-        <v>4.045453671885394</v>
+        <v>3.912928582185648</v>
       </c>
       <c r="D84">
-        <v>15.0642536718854</v>
+        <v>15.08012858218565</v>
       </c>
       <c r="E84">
-        <v>9.428800000000001</v>
+        <v>9.577200000000001</v>
       </c>
       <c r="F84">
-        <v>12.1688</v>
+        <v>12.3172</v>
       </c>
       <c r="G84">
         <v>1.15</v>
@@ -8523,28 +8523,28 @@
         <v>3.723</v>
       </c>
       <c r="M84">
-        <v>0.67293464</v>
+        <v>0.6811411600000001</v>
       </c>
       <c r="N84">
-        <v>3.05006536</v>
+        <v>3.04185884</v>
       </c>
       <c r="O84">
-        <v>0.610013072</v>
+        <v>0.608371768</v>
       </c>
       <c r="P84">
-        <v>2.440052288</v>
+        <v>2.433487072</v>
       </c>
       <c r="Q84">
-        <v>2.447052288</v>
+        <v>2.440487072</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3935264901282924</v>
+        <v>0.4131001737831358</v>
       </c>
       <c r="T84">
-        <v>3.807747591621878</v>
+        <v>4.022087450424123</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.532483808531538</v>
+        <v>5.465827377103447</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8569,22 +8569,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1069462295431331</v>
+        <v>0.1067808908631735</v>
       </c>
       <c r="C85">
-        <v>3.912928582185648</v>
+        <v>3.780436986163997</v>
       </c>
       <c r="D85">
-        <v>15.08012858218565</v>
+        <v>15.096036986164</v>
       </c>
       <c r="E85">
-        <v>9.577200000000001</v>
+        <v>9.7256</v>
       </c>
       <c r="F85">
-        <v>12.3172</v>
+        <v>12.4656</v>
       </c>
       <c r="G85">
         <v>1.15</v>
@@ -8605,28 +8605,28 @@
         <v>3.723</v>
       </c>
       <c r="M85">
-        <v>0.6811411600000001</v>
+        <v>0.68934768</v>
       </c>
       <c r="N85">
-        <v>3.04185884</v>
+        <v>3.03365232</v>
       </c>
       <c r="O85">
-        <v>0.608371768</v>
+        <v>0.606730464</v>
       </c>
       <c r="P85">
-        <v>2.433487072</v>
+        <v>2.426921856</v>
       </c>
       <c r="Q85">
-        <v>2.440487072</v>
+        <v>2.433921856</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4131001737831358</v>
+        <v>0.4351205678948347</v>
       </c>
       <c r="T85">
-        <v>4.022087450424123</v>
+        <v>4.263219791576649</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.465827377103447</v>
+        <v>5.400758003566501</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8651,22 +8651,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1067808908631735</v>
+        <v>0.106615552183214</v>
       </c>
       <c r="C86">
-        <v>3.780436986163997</v>
+        <v>3.647978989932328</v>
       </c>
       <c r="D86">
-        <v>15.096036986164</v>
+        <v>15.11197898993233</v>
       </c>
       <c r="E86">
-        <v>9.7256</v>
+        <v>9.873999999999999</v>
       </c>
       <c r="F86">
-        <v>12.4656</v>
+        <v>12.614</v>
       </c>
       <c r="G86">
         <v>1.15</v>
@@ -8687,28 +8687,28 @@
         <v>3.723</v>
       </c>
       <c r="M86">
-        <v>0.68934768</v>
+        <v>0.6975542</v>
       </c>
       <c r="N86">
-        <v>3.03365232</v>
+        <v>3.0254458</v>
       </c>
       <c r="O86">
-        <v>0.606730464</v>
+        <v>0.60508916</v>
       </c>
       <c r="P86">
-        <v>2.426921856</v>
+        <v>2.42035664</v>
       </c>
       <c r="Q86">
-        <v>2.433921856</v>
+        <v>2.42735664</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4351205678948344</v>
+        <v>0.4600770145547597</v>
       </c>
       <c r="T86">
-        <v>4.263219791576646</v>
+        <v>4.536503111549509</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.400758003566501</v>
+        <v>5.337219674112778</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8733,22 +8733,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.106615552183214</v>
+        <v>0.1064502135032544</v>
       </c>
       <c r="C87">
-        <v>3.647978989932328</v>
+        <v>3.51555470005124</v>
       </c>
       <c r="D87">
-        <v>15.11197898993233</v>
+        <v>15.12795470005124</v>
       </c>
       <c r="E87">
-        <v>9.873999999999999</v>
+        <v>10.0224</v>
       </c>
       <c r="F87">
-        <v>12.614</v>
+        <v>12.7624</v>
       </c>
       <c r="G87">
         <v>1.15</v>
@@ -8769,28 +8769,28 @@
         <v>3.723</v>
       </c>
       <c r="M87">
-        <v>0.6975542</v>
+        <v>0.70576072</v>
       </c>
       <c r="N87">
-        <v>3.0254458</v>
+        <v>3.01723928</v>
       </c>
       <c r="O87">
-        <v>0.60508916</v>
+        <v>0.6034478560000001</v>
       </c>
       <c r="P87">
-        <v>2.42035664</v>
+        <v>2.413791424</v>
       </c>
       <c r="Q87">
-        <v>2.42735664</v>
+        <v>2.420791424</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4600770145547597</v>
+        <v>0.4885986678803886</v>
       </c>
       <c r="T87">
-        <v>4.536503111549509</v>
+        <v>4.848826905804208</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.337219674112778</v>
+        <v>5.275158980227746</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8815,22 +8815,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1064502135032544</v>
+        <v>0.1062848748232948</v>
       </c>
       <c r="C88">
-        <v>3.51555470005124</v>
+        <v>3.383164223532424</v>
       </c>
       <c r="D88">
-        <v>15.12795470005124</v>
+        <v>15.14396422353242</v>
       </c>
       <c r="E88">
-        <v>10.0224</v>
+        <v>10.1708</v>
       </c>
       <c r="F88">
-        <v>12.7624</v>
+        <v>12.9108</v>
       </c>
       <c r="G88">
         <v>1.15</v>
@@ -8851,28 +8851,28 @@
         <v>3.723</v>
       </c>
       <c r="M88">
-        <v>0.70576072</v>
+        <v>0.71396724</v>
       </c>
       <c r="N88">
-        <v>3.01723928</v>
+        <v>3.00903276</v>
       </c>
       <c r="O88">
-        <v>0.6034478560000001</v>
+        <v>0.601806552</v>
       </c>
       <c r="P88">
-        <v>2.413791424</v>
+        <v>2.407226208</v>
       </c>
       <c r="Q88">
-        <v>2.420791424</v>
+        <v>2.414226208</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4885986678803886</v>
+        <v>0.5215082678714987</v>
       </c>
       <c r="T88">
-        <v>4.848826905804208</v>
+        <v>5.20920051455963</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8889,7 +8889,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.275158980227746</v>
+        <v>5.21452496896076</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8897,22 +8897,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1062848748232948</v>
+        <v>0.1061195361433353</v>
       </c>
       <c r="C89">
-        <v>3.383164223532424</v>
+        <v>3.250807667841009</v>
       </c>
       <c r="D89">
-        <v>15.14396422353242</v>
+        <v>15.16000766784101</v>
       </c>
       <c r="E89">
-        <v>10.1708</v>
+        <v>10.3192</v>
       </c>
       <c r="F89">
-        <v>12.9108</v>
+        <v>13.0592</v>
       </c>
       <c r="G89">
         <v>1.15</v>
@@ -8933,28 +8933,28 @@
         <v>3.723</v>
       </c>
       <c r="M89">
-        <v>0.71396724</v>
+        <v>0.7221737600000001</v>
       </c>
       <c r="N89">
-        <v>3.00903276</v>
+        <v>3.00082624</v>
       </c>
       <c r="O89">
-        <v>0.601806552</v>
+        <v>0.600165248</v>
       </c>
       <c r="P89">
-        <v>2.407226208</v>
+        <v>2.400660992</v>
       </c>
       <c r="Q89">
-        <v>2.414226208</v>
+        <v>2.407660992</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5215082678714987</v>
+        <v>0.5599028011944608</v>
       </c>
       <c r="T89">
-        <v>5.20920051455963</v>
+        <v>5.629636391440957</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8971,7 +8971,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.21452496896076</v>
+        <v>5.155269003404388</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8979,22 +8979,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1061195361433353</v>
+        <v>0.1059541974633758</v>
       </c>
       <c r="C90">
-        <v>3.250807667841009</v>
+        <v>3.118485140898034</v>
       </c>
       <c r="D90">
-        <v>15.16000766784101</v>
+        <v>15.17608514089803</v>
       </c>
       <c r="E90">
-        <v>10.3192</v>
+        <v>10.4676</v>
       </c>
       <c r="F90">
-        <v>13.0592</v>
+        <v>13.2076</v>
       </c>
       <c r="G90">
         <v>1.15</v>
@@ -9015,28 +9015,28 @@
         <v>3.723</v>
       </c>
       <c r="M90">
-        <v>0.7221737600000001</v>
+        <v>0.73038028</v>
       </c>
       <c r="N90">
-        <v>3.00082624</v>
+        <v>2.99261972</v>
       </c>
       <c r="O90">
-        <v>0.600165248</v>
+        <v>0.598523944</v>
       </c>
       <c r="P90">
-        <v>2.400660992</v>
+        <v>2.394095776</v>
       </c>
       <c r="Q90">
-        <v>2.407660992</v>
+        <v>2.401095776</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5599028011944608</v>
+        <v>0.6052781587579614</v>
       </c>
       <c r="T90">
-        <v>5.629636391440957</v>
+        <v>6.126515155027979</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.155269003404388</v>
+        <v>5.09734463257962</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9061,22 +9061,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1059541974633758</v>
+        <v>0.1057888587834162</v>
       </c>
       <c r="C91">
-        <v>3.118485140898034</v>
+        <v>2.986196751082813</v>
       </c>
       <c r="D91">
-        <v>15.17608514089803</v>
+        <v>15.19219675108281</v>
       </c>
       <c r="E91">
-        <v>10.4676</v>
+        <v>10.616</v>
       </c>
       <c r="F91">
-        <v>13.2076</v>
+        <v>13.356</v>
       </c>
       <c r="G91">
         <v>1.15</v>
@@ -9097,28 +9097,28 @@
         <v>3.723</v>
       </c>
       <c r="M91">
-        <v>0.73038028</v>
+        <v>0.7385868</v>
       </c>
       <c r="N91">
-        <v>2.99261972</v>
+        <v>2.9844132</v>
       </c>
       <c r="O91">
-        <v>0.598523944</v>
+        <v>0.5968826399999999</v>
       </c>
       <c r="P91">
-        <v>2.394095776</v>
+        <v>2.38753056</v>
       </c>
       <c r="Q91">
-        <v>2.401095776</v>
+        <v>2.39453056</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6052781587579614</v>
+        <v>0.6597285878341621</v>
       </c>
       <c r="T91">
-        <v>6.126515155027979</v>
+        <v>6.722769671332407</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.09734463257962</v>
+        <v>5.040707469995402</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9143,22 +9143,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1057888587834162</v>
+        <v>0.1056235201034566</v>
       </c>
       <c r="C92">
-        <v>2.986196751082813</v>
+        <v>2.853942607235407</v>
       </c>
       <c r="D92">
-        <v>15.19219675108281</v>
+        <v>15.20834260723541</v>
       </c>
       <c r="E92">
-        <v>10.616</v>
+        <v>10.7644</v>
       </c>
       <c r="F92">
-        <v>13.356</v>
+        <v>13.5044</v>
       </c>
       <c r="G92">
         <v>1.15</v>
@@ -9179,28 +9179,28 @@
         <v>3.723</v>
       </c>
       <c r="M92">
-        <v>0.7385868</v>
+        <v>0.7467933200000001</v>
       </c>
       <c r="N92">
-        <v>2.9844132</v>
+        <v>2.97620668</v>
       </c>
       <c r="O92">
-        <v>0.5968826399999999</v>
+        <v>0.595241336</v>
       </c>
       <c r="P92">
-        <v>2.38753056</v>
+        <v>2.380965344</v>
       </c>
       <c r="Q92">
-        <v>2.39453056</v>
+        <v>2.387965344</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6597285878341621</v>
+        <v>0.7262791122606296</v>
       </c>
       <c r="T92">
-        <v>6.722769671332407</v>
+        <v>7.451525191260039</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -9217,7 +9217,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.040707469995402</v>
+        <v>4.985315080215232</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9225,22 +9225,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1056235201034566</v>
+        <v>0.1054581814234971</v>
       </c>
       <c r="C93">
-        <v>2.853942607235407</v>
+        <v>2.72172281865903</v>
       </c>
       <c r="D93">
-        <v>15.20834260723541</v>
+        <v>15.22452281865903</v>
       </c>
       <c r="E93">
-        <v>10.7644</v>
+        <v>10.9128</v>
       </c>
       <c r="F93">
-        <v>13.5044</v>
+        <v>13.6528</v>
       </c>
       <c r="G93">
         <v>1.15</v>
@@ -9261,28 +9261,28 @@
         <v>3.723</v>
       </c>
       <c r="M93">
-        <v>0.7467933200000001</v>
+        <v>0.7549998400000001</v>
       </c>
       <c r="N93">
-        <v>2.97620668</v>
+        <v>2.96800016</v>
       </c>
       <c r="O93">
-        <v>0.595241336</v>
+        <v>0.593600032</v>
       </c>
       <c r="P93">
-        <v>2.380965344</v>
+        <v>2.374400128</v>
       </c>
       <c r="Q93">
-        <v>2.387965344</v>
+        <v>2.381400128</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7262791122606296</v>
+        <v>0.8094672677937141</v>
       </c>
       <c r="T93">
-        <v>7.451525191260039</v>
+        <v>8.362469591169582</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.985315080215232</v>
+        <v>4.931126872821588</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9307,22 +9307,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1054581814234971</v>
+        <v>0.1052928427435375</v>
       </c>
       <c r="C94">
-        <v>2.72172281865903</v>
+        <v>2.589537495122578</v>
       </c>
       <c r="D94">
-        <v>15.22452281865903</v>
+        <v>15.24073749512258</v>
       </c>
       <c r="E94">
-        <v>10.9128</v>
+        <v>11.0612</v>
       </c>
       <c r="F94">
-        <v>13.6528</v>
+        <v>13.8012</v>
       </c>
       <c r="G94">
         <v>1.15</v>
@@ -9343,28 +9343,28 @@
         <v>3.723</v>
       </c>
       <c r="M94">
-        <v>0.7549998400000001</v>
+        <v>0.7632063600000001</v>
       </c>
       <c r="N94">
-        <v>2.96800016</v>
+        <v>2.95979364</v>
       </c>
       <c r="O94">
-        <v>0.593600032</v>
+        <v>0.591958728</v>
       </c>
       <c r="P94">
-        <v>2.374400128</v>
+        <v>2.367834912</v>
       </c>
       <c r="Q94">
-        <v>2.381400128</v>
+        <v>2.374834912</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8094672677937141</v>
+        <v>0.9164234677648226</v>
       </c>
       <c r="T94">
-        <v>8.362469591169582</v>
+        <v>9.533683819624706</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9381,7 +9381,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.931126872821588</v>
+        <v>4.878104003221356</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9389,22 +9389,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1052928427435375</v>
+        <v>0.105127504063578</v>
       </c>
       <c r="C95">
-        <v>2.589537495122578</v>
+        <v>2.457386746863058</v>
       </c>
       <c r="D95">
-        <v>15.24073749512258</v>
+        <v>15.25698674686306</v>
       </c>
       <c r="E95">
-        <v>11.0612</v>
+        <v>11.2096</v>
       </c>
       <c r="F95">
-        <v>13.8012</v>
+        <v>13.9496</v>
       </c>
       <c r="G95">
         <v>1.15</v>
@@ -9425,28 +9425,28 @@
         <v>3.723</v>
       </c>
       <c r="M95">
-        <v>0.7632063600000001</v>
+        <v>0.7714128800000001</v>
       </c>
       <c r="N95">
-        <v>2.95979364</v>
+        <v>2.95158712</v>
       </c>
       <c r="O95">
-        <v>0.591958728</v>
+        <v>0.590317424</v>
       </c>
       <c r="P95">
-        <v>2.367834912</v>
+        <v>2.361269696</v>
       </c>
       <c r="Q95">
-        <v>2.374834912</v>
+        <v>2.368269696</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9164234677648226</v>
+        <v>1.059031734392967</v>
       </c>
       <c r="T95">
-        <v>9.533683819624706</v>
+        <v>11.09530279089821</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9463,7 +9463,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.878104003221356</v>
+        <v>4.826209279782831</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9471,22 +9471,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.105127504063578</v>
+        <v>0.1049621653836185</v>
       </c>
       <c r="C96">
-        <v>2.457386746863058</v>
+        <v>2.325270684588096</v>
       </c>
       <c r="D96">
-        <v>15.25698674686306</v>
+        <v>15.2732706845881</v>
       </c>
       <c r="E96">
-        <v>11.2096</v>
+        <v>11.358</v>
       </c>
       <c r="F96">
-        <v>13.9496</v>
+        <v>14.098</v>
       </c>
       <c r="G96">
         <v>1.15</v>
@@ -9507,28 +9507,28 @@
         <v>3.723</v>
       </c>
       <c r="M96">
-        <v>0.7714128800000001</v>
+        <v>0.7796194000000001</v>
       </c>
       <c r="N96">
-        <v>2.95158712</v>
+        <v>2.9433806</v>
       </c>
       <c r="O96">
-        <v>0.590317424</v>
+        <v>0.58867612</v>
       </c>
       <c r="P96">
-        <v>2.361269696</v>
+        <v>2.35470448</v>
       </c>
       <c r="Q96">
-        <v>2.368269696</v>
+        <v>2.36170448</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.059031734392967</v>
+        <v>1.258683307672371</v>
       </c>
       <c r="T96">
-        <v>11.09530279089821</v>
+        <v>13.28156935068111</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.826209279782831</v>
+        <v>4.775407076837748</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9553,22 +9553,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1049621653836185</v>
+        <v>0.1047968267036589</v>
       </c>
       <c r="C97">
-        <v>2.325270684588096</v>
+        <v>2.19318941947849</v>
       </c>
       <c r="D97">
-        <v>15.2732706845881</v>
+        <v>15.28958941947849</v>
       </c>
       <c r="E97">
-        <v>11.358</v>
+        <v>11.5064</v>
       </c>
       <c r="F97">
-        <v>14.098</v>
+        <v>14.2464</v>
       </c>
       <c r="G97">
         <v>1.15</v>
@@ -9589,28 +9589,28 @@
         <v>3.723</v>
       </c>
       <c r="M97">
-        <v>0.7796194000000001</v>
+        <v>0.7878259200000001</v>
       </c>
       <c r="N97">
-        <v>2.9433806</v>
+        <v>2.93517408</v>
       </c>
       <c r="O97">
-        <v>0.58867612</v>
+        <v>0.587034816</v>
       </c>
       <c r="P97">
-        <v>2.35470448</v>
+        <v>2.348139264</v>
       </c>
       <c r="Q97">
-        <v>2.36170448</v>
+        <v>2.355139264</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.258683307672371</v>
+        <v>1.558160667591475</v>
       </c>
       <c r="T97">
-        <v>13.28156935068111</v>
+        <v>16.56096919035546</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9627,7 +9627,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.775407076837748</v>
+        <v>4.725663253120689</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9635,22 +9635,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1047968267036589</v>
+        <v>0.1046314880236993</v>
       </c>
       <c r="C98">
-        <v>2.193189419478491</v>
+        <v>2.061143063190684</v>
       </c>
       <c r="D98">
-        <v>15.28958941947849</v>
+        <v>15.30594306319068</v>
       </c>
       <c r="E98">
-        <v>11.5064</v>
+        <v>11.6548</v>
       </c>
       <c r="F98">
-        <v>14.2464</v>
+        <v>14.3948</v>
       </c>
       <c r="G98">
         <v>1.15</v>
@@ -9671,28 +9671,28 @@
         <v>3.723</v>
       </c>
       <c r="M98">
-        <v>0.78782592</v>
+        <v>0.7960324400000001</v>
       </c>
       <c r="N98">
-        <v>2.93517408</v>
+        <v>2.92696756</v>
       </c>
       <c r="O98">
-        <v>0.587034816</v>
+        <v>0.5853935119999999</v>
       </c>
       <c r="P98">
-        <v>2.348139264</v>
+        <v>2.341574048</v>
       </c>
       <c r="Q98">
-        <v>2.355139264</v>
+        <v>2.348574048</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.558160667591471</v>
+        <v>2.057289600789976</v>
       </c>
       <c r="T98">
-        <v>16.56096919035542</v>
+        <v>22.02663558981266</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.72566325312069</v>
+        <v>4.676945075253466</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9717,22 +9717,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1046314880236993</v>
+        <v>0.1044661493437398</v>
       </c>
       <c r="C99">
-        <v>2.061143063190684</v>
+        <v>1.929131727859353</v>
       </c>
       <c r="D99">
-        <v>15.30594306319068</v>
+        <v>15.32233172785935</v>
       </c>
       <c r="E99">
-        <v>11.6548</v>
+        <v>11.8032</v>
       </c>
       <c r="F99">
-        <v>14.3948</v>
+        <v>14.5432</v>
       </c>
       <c r="G99">
         <v>1.15</v>
@@ -9753,28 +9753,28 @@
         <v>3.723</v>
       </c>
       <c r="M99">
-        <v>0.7960324400000001</v>
+        <v>0.8042389599999999</v>
       </c>
       <c r="N99">
-        <v>2.92696756</v>
+        <v>2.91876104</v>
       </c>
       <c r="O99">
-        <v>0.5853935119999999</v>
+        <v>0.5837522079999999</v>
       </c>
       <c r="P99">
-        <v>2.341574048</v>
+        <v>2.335008832</v>
       </c>
       <c r="Q99">
-        <v>2.348574048</v>
+        <v>2.342008832</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.057289600789976</v>
+        <v>3.055547467186986</v>
       </c>
       <c r="T99">
-        <v>22.02663558981266</v>
+        <v>32.95796838872712</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.676945075253466</v>
+        <v>4.629221145914144</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9799,22 +9799,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1044661493437398</v>
+        <v>0.1043008106637802</v>
       </c>
       <c r="C100">
-        <v>1.929131727859353</v>
+        <v>1.797155526099951</v>
       </c>
       <c r="D100">
-        <v>15.32233172785935</v>
+        <v>15.33875552609995</v>
       </c>
       <c r="E100">
-        <v>11.8032</v>
+        <v>11.9516</v>
       </c>
       <c r="F100">
-        <v>14.5432</v>
+        <v>14.6916</v>
       </c>
       <c r="G100">
         <v>1.15</v>
@@ -9835,28 +9835,28 @@
         <v>3.723</v>
       </c>
       <c r="M100">
-        <v>0.8042389599999999</v>
+        <v>0.8124454799999999</v>
       </c>
       <c r="N100">
-        <v>2.91876104</v>
+        <v>2.91055452</v>
       </c>
       <c r="O100">
-        <v>0.5837522079999999</v>
+        <v>0.582110904</v>
       </c>
       <c r="P100">
-        <v>2.335008832</v>
+        <v>2.328443616</v>
       </c>
       <c r="Q100">
-        <v>2.342008832</v>
+        <v>2.335443616</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.055547467186986</v>
+        <v>6.050321066378017</v>
       </c>
       <c r="T100">
-        <v>32.95796838872712</v>
+        <v>65.75196678547053</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9873,91 +9873,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.629221145914144</v>
+        <v>4.582461336359456</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1043008106637802</v>
-      </c>
-      <c r="C101">
-        <v>1.797155526099951</v>
-      </c>
-      <c r="D101">
-        <v>15.33875552609995</v>
-      </c>
-      <c r="E101">
-        <v>11.9516</v>
-      </c>
-      <c r="F101">
-        <v>14.6916</v>
-      </c>
-      <c r="G101">
-        <v>1.15</v>
-      </c>
-      <c r="H101">
-        <v>12.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.73</v>
-      </c>
-      <c r="K101">
-        <v>0.007</v>
-      </c>
-      <c r="L101">
-        <v>3.723</v>
-      </c>
-      <c r="M101">
-        <v>0.8124454799999999</v>
-      </c>
-      <c r="N101">
-        <v>2.91055452</v>
-      </c>
-      <c r="O101">
-        <v>0.582110904</v>
-      </c>
-      <c r="P101">
-        <v>2.328443616</v>
-      </c>
-      <c r="Q101">
-        <v>2.335443616</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.050321066378017</v>
-      </c>
-      <c r="T101">
-        <v>65.75196678547053</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.04424</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.582461336359456</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
